--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_39.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3464467.791120002</v>
+        <v>3495071.453489787</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11458411.28550863</v>
+        <v>11461563.12389249</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11458411.28550863</v>
+        <v>11461563.12389249</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7347049.384398957</v>
+        <v>7352335.338032163</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7347049.384398957</v>
+        <v>7352335.338032163</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48752370.86521418</v>
+        <v>48755083.46939722</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>405.1726160150884</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -681,10 +681,10 @@
         <v>681.1694999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>626.4761708542713</v>
       </c>
       <c r="L2" t="n">
-        <v>13.1534305042963</v>
+        <v>4.499525720857433</v>
       </c>
       <c r="M2" t="n">
         <v>84.40122279550246</v>
@@ -696,7 +696,7 @@
         <v>674.4840806293688</v>
       </c>
       <c r="P2" t="n">
-        <v>617.8222660708323</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>681.1694999999999</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>482.5726904153883</v>
+        <v>82.57269041538825</v>
       </c>
       <c r="T2" t="n">
-        <v>184.3174510752975</v>
+        <v>584.3174510752975</v>
       </c>
       <c r="U2" t="n">
-        <v>572.3515041307376</v>
+        <v>249.1782010712237</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>97.44332101822825</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>61.21032071932831</v>
       </c>
       <c r="T3" t="n">
-        <v>4.19601050053268</v>
+        <v>198.621958929508</v>
       </c>
       <c r="U3" t="n">
-        <v>400.1913974960358</v>
+        <v>0.1913974960357905</v>
       </c>
       <c r="V3" t="n">
         <v>414.5106671915202</v>
@@ -860,7 +860,7 @@
         <v>305.605266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>203.7998595757635</v>
+        <v>203.7998595757558</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -906,19 +906,19 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.218678819679527</v>
+        <v>109.3520865684866</v>
       </c>
       <c r="H5" t="n">
-        <v>402.4927642311656</v>
+        <v>2.492764231165601</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>129.3131797831871</v>
       </c>
       <c r="J5" t="n">
         <v>254.0173349855667</v>
       </c>
       <c r="K5" t="n">
-        <v>317.0785414271741</v>
+        <v>626.4761708542713</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -933,7 +933,7 @@
         <v>674.4840806293688</v>
       </c>
       <c r="P5" t="n">
-        <v>617.8222660708323</v>
+        <v>308.4246366437351</v>
       </c>
       <c r="Q5" t="n">
         <v>193.7977768870575</v>
@@ -942,10 +942,10 @@
         <v>217.0398953107065</v>
       </c>
       <c r="S5" t="n">
-        <v>482.5726904153883</v>
+        <v>82.57269041538822</v>
       </c>
       <c r="T5" t="n">
-        <v>419.764038607292</v>
+        <v>184.3174510752976</v>
       </c>
       <c r="U5" t="n">
         <v>249.1782010712237</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82.6084848984205</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>136.2874160338758</v>
       </c>
       <c r="R6" t="n">
         <v>129.3784765376623</v>
@@ -1033,13 +1033,13 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>52.11830564113046</v>
       </c>
     </row>
     <row r="7">
@@ -1097,7 +1097,7 @@
         <v>305.605266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>203.7998595757649</v>
+        <v>203.7998595757713</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
@@ -1143,22 +1143,22 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.218678819679553</v>
+        <v>403.2186788196796</v>
       </c>
       <c r="H8" t="n">
-        <v>402.4927642311656</v>
+        <v>2.492764231165609</v>
       </c>
       <c r="I8" t="n">
         <v>129.3131797831871</v>
       </c>
       <c r="J8" t="n">
-        <v>681.1694999999999</v>
+        <v>254.0173349855667</v>
       </c>
       <c r="K8" t="n">
-        <v>626.4761708542713</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>491.8712488337996</v>
+        <v>609.9901306532662</v>
       </c>
       <c r="M8" t="n">
         <v>84.40122279550246</v>
@@ -1170,10 +1170,10 @@
         <v>674.4840806293688</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>617.8222660708323</v>
       </c>
       <c r="Q8" t="n">
-        <v>193.7977768870575</v>
+        <v>511.4849648654632</v>
       </c>
       <c r="R8" t="n">
         <v>217.0398953107065</v>
@@ -1182,10 +1182,10 @@
         <v>82.57269041538825</v>
       </c>
       <c r="T8" t="n">
-        <v>290.4508588241044</v>
+        <v>584.3174510752975</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1782010712237</v>
+        <v>355.3116088200313</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>224.0543246605925</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -1219,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.451309459933</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>136.2874160338758</v>
       </c>
       <c r="R9" t="n">
         <v>129.3784765376623</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>58.13853239509934</v>
       </c>
     </row>
     <row r="10">
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>82.75354582877941</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>134.2076654356193</v>
       </c>
       <c r="O10" t="n">
-        <v>203.799859575755</v>
+        <v>206.2909411281953</v>
       </c>
       <c r="P10" t="n">
-        <v>258.2227170004086</v>
+        <v>28.63854623457819</v>
       </c>
       <c r="Q10" t="n">
-        <v>305.605266425598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>315.7371443745936</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>191.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>190.2186788196795</v>
@@ -1419,10 +1419,10 @@
         <v>269.5726904153883</v>
       </c>
       <c r="T11" t="n">
-        <v>334.195600145881</v>
+        <v>371.3174510752975</v>
       </c>
       <c r="U11" t="n">
-        <v>436.1782010712237</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>379.2818334606677</v>
+        <v>288.1311222116569</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>298.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>15.25655591220722</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>269.7535458287794</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>285.0101017409866</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>264.9993129555745</v>
+        <v>263.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>231.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>14.07183340894406</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1650,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.03989531070652674</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>128.7973732959519</v>
+        <v>264.5726904153883</v>
       </c>
       <c r="T14" t="n">
-        <v>367.3174510752975</v>
+        <v>366.3174510752975</v>
       </c>
       <c r="U14" t="n">
-        <v>432.1782010712237</v>
+        <v>431.1782010712237</v>
       </c>
       <c r="V14" t="n">
-        <v>412.8510241668239</v>
+        <v>411.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>421.3734759809475</v>
+        <v>420.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>375.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>294.3174326828064</v>
+        <v>293.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>167.5565566463266</v>
+        <v>166.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>144.0999124455193</v>
+        <v>143.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>130.9376868977026</v>
+        <v>129.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>125.6720972219126</v>
+        <v>124.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>122.6362423378769</v>
+        <v>121.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>108.451309459933</v>
+        <v>107.451309459933</v>
       </c>
       <c r="H15" t="n">
-        <v>112.3844268090626</v>
+        <v>111.3844268090626</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>312.3784765376623</v>
+        <v>311.3784765376623</v>
       </c>
       <c r="S15" t="n">
-        <v>244.2103207193283</v>
+        <v>243.2103207193283</v>
       </c>
       <c r="T15" t="n">
-        <v>187.1960105005327</v>
+        <v>186.1960105005327</v>
       </c>
       <c r="U15" t="n">
-        <v>183.1913974960358</v>
+        <v>182.1913974960358</v>
       </c>
       <c r="V15" t="n">
-        <v>197.5106671915202</v>
+        <v>196.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>215.3731429098285</v>
+        <v>214.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>202.8627394453875</v>
+        <v>201.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>182.3913927661343</v>
+        <v>181.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.622732658995668</v>
+        <v>8.622732658995668</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>312.6121017409866</v>
+        <v>319.5126017409866</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>9.372809838709685</v>
+        <v>8.372809838709685</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>102.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>60.8497724495697</v>
+        <v>96.36328960686865</v>
       </c>
       <c r="F17" t="n">
         <v>96.88962870801186</v>
@@ -1899,7 +1899,7 @@
         <v>341.1782010712237</v>
       </c>
       <c r="V17" t="n">
-        <v>321.8510241668239</v>
+        <v>286.3375070095249</v>
       </c>
       <c r="W17" t="n">
         <v>330.3734759809475</v>
@@ -1921,7 +1921,7 @@
         <v>76.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>53.09991244551929</v>
+        <v>324.9701655256061</v>
       </c>
       <c r="D18" t="n">
         <v>39.93768689770263</v>
@@ -1969,7 +1969,7 @@
         <v>221.3784765376623</v>
       </c>
       <c r="S18" t="n">
-        <v>425.0805737994149</v>
+        <v>153.2103207193283</v>
       </c>
       <c r="T18" t="n">
         <v>96.19601050053268</v>
@@ -2027,28 +2027,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>79.62244782991033</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>174.7535458287794</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>226.2076654356193</v>
       </c>
       <c r="O19" t="n">
-        <v>106.262801141336</v>
+        <v>298.2909411281953</v>
       </c>
       <c r="P19" t="n">
         <v>350.2227170004086</v>
       </c>
       <c r="Q19" t="n">
-        <v>397.605266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>407.7371443745937</v>
+        <v>82.56824677026631</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>50.16236494875707</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>141.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>66.82563858255082</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E20" t="n">
         <v>96.36328960686865</v>
@@ -2139,7 +2139,7 @@
         <v>321.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>330.3734759809475</v>
+        <v>294.8599588236486</v>
       </c>
       <c r="X20" t="n">
         <v>284.2818334606677</v>
@@ -2167,7 +2167,7 @@
         <v>34.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>167.2190793840876</v>
+        <v>31.63624233787687</v>
       </c>
       <c r="G21" t="n">
         <v>17.451309459933</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>136.2874160338758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>221.3784765376623</v>
@@ -2209,7 +2209,7 @@
         <v>153.2103207193283</v>
       </c>
       <c r="T21" t="n">
-        <v>96.19601050053268</v>
+        <v>368.0662635806192</v>
       </c>
       <c r="U21" t="n">
         <v>92.1913974960358</v>
@@ -2267,22 +2267,22 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>174.7535458287794</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>226.2076654356193</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>298.2909411281953</v>
       </c>
       <c r="P22" t="n">
-        <v>350.2227170004086</v>
+        <v>158.1945770135491</v>
       </c>
       <c r="Q22" t="n">
         <v>397.605266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>113.0387342515311</v>
+        <v>407.7371443745937</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>96.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>95.21867881967952</v>
+        <v>79.10916166238046</v>
       </c>
       <c r="H23" t="n">
-        <v>94.49276423116559</v>
+        <v>94.49276423116561</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>173.9863732580895</v>
+        <v>174.5726904153883</v>
       </c>
       <c r="T23" t="n">
         <v>276.3174510752975</v>
@@ -2401,16 +2401,16 @@
         <v>39.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>34.67209722191262</v>
+        <v>306.5423503019996</v>
       </c>
       <c r="F24" t="n">
         <v>31.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>17.451309459933</v>
+        <v>17.45130945993299</v>
       </c>
       <c r="H24" t="n">
-        <v>21.38442680906264</v>
+        <v>21.38442680906263</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>96.19601050053268</v>
       </c>
       <c r="U24" t="n">
-        <v>92.1913974960358</v>
+        <v>92.19139749603579</v>
       </c>
       <c r="V24" t="n">
         <v>106.5106671915202</v>
@@ -2458,7 +2458,7 @@
         <v>124.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>383.7329925254743</v>
+        <v>111.8627394453875</v>
       </c>
       <c r="Y24" t="n">
         <v>91.39139276613435</v>
@@ -2504,22 +2504,22 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>174.7535458287794</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>226.2076654356193</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>298.2909411281953</v>
+        <v>106.2628011413362</v>
       </c>
       <c r="P25" t="n">
         <v>350.2227170004086</v>
       </c>
       <c r="Q25" t="n">
-        <v>212.353059548934</v>
+        <v>397.605266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>407.7371443745936</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2556,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>193.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>185.4927642311656</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2610,16 +2610,16 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>398.0000000000078</v>
+        <v>219.3109305157701</v>
       </c>
       <c r="W26" t="n">
-        <v>134.7964432276022</v>
+        <v>398.000000000031</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>294.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2632,7 +2632,7 @@
         <v>167.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>144.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>130.9376868977026</v>
@@ -2641,13 +2641,13 @@
         <v>125.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>122.6362423378769</v>
+        <v>23.1399393889284</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>112.3844268090626</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2680,10 +2680,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>119.4151931880589</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>187.1960105005327</v>
       </c>
       <c r="U27" t="n">
         <v>183.1913974960358</v>
@@ -2708,16 +2708,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>55.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>45.61068980710627</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9.622732658995659</v>
+        <v>9.622732658995668</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2756,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>312.6121017409867</v>
       </c>
       <c r="S28" t="n">
-        <v>141.1623649487571</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>238.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2796,13 +2796,13 @@
         <v>167.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>161.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>161.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>160.2186788196796</v>
       </c>
       <c r="H29" t="n">
         <v>159.4927642311656</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>142.6950707481217</v>
+        <v>142.6950707486894</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2838,16 +2838,16 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>239.5726904153883</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>269.194457919081</v>
       </c>
       <c r="U29" t="n">
-        <v>398.0000000000102</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>257.4742487585374</v>
+        <v>386.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -2875,16 +2875,16 @@
         <v>104.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>99.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>96.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>82.451309459933</v>
+        <v>82.45130945993299</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>86.38442680906263</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>91.34005800396835</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>171.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>78.05238759113627</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>176.8627394453875</v>
@@ -2978,22 +2978,22 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>200.1606476010717</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>291.2076654356193</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>93.36831303668131</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>398.0000000000097</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3027,22 +3027,22 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>206.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>167.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>161.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>161.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>160.2186788196795</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>39.28961230228015</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>142.6950707486747</v>
       </c>
       <c r="L32" t="n">
-        <v>142.6950707481504</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>239.5726904153882</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>157.7719238927527</v>
+        <v>386.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>395.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>349.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>268.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3109,7 +3109,7 @@
         <v>118.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>96.60564767977615</v>
+        <v>104.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>99.67209722191262</v>
@@ -3118,10 +3118,10 @@
         <v>96.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>82.45130945993299</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>86.38442680906263</v>
+        <v>86.38442680906265</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3166,7 +3166,7 @@
         <v>171.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>74.11927024198849</v>
       </c>
       <c r="X33" t="n">
         <v>176.8627394453875</v>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>31.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>17.52010421948155</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>398.0000000000052</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>398.0000000000097</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>93.36831303668129</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>44.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>238.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>206.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>167.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>144.7346337087543</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>142.6950707481525</v>
+        <v>142.6950707487327</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3312,22 +3312,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>239.5726904153883</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>398.0000000000102</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>386.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>395.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>25.85522996339488</v>
+        <v>349.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>268.3174326828064</v>
@@ -3403,13 +3403,13 @@
         <v>171.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>148.0593535482079</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>176.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>148.0593535481899</v>
       </c>
     </row>
     <row r="37">
@@ -3464,13 +3464,13 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>93.36831303668581</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>398.0000000000052</v>
+        <v>376.2059480879338</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>115.1623649487571</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,16 +3498,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>238.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>206.4745782429939</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>167.3391557398498</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>161.3632896068686</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>143.9583488725009</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>142.6950707486655</v>
       </c>
       <c r="L38" t="n">
-        <v>142.6950707481532</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3549,19 +3549,19 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>239.5726904153883</v>
+        <v>239.5726904153882</v>
       </c>
       <c r="T38" t="n">
-        <v>341.3174510752975</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>398.0000000000125</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>170.2947825283721</v>
+        <v>386.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>395.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3583,19 +3583,19 @@
         <v>118.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>104.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>99.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>96.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>82.451309459933</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>78.05238759111813</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>54.16625987940467</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>218.2103207193283</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>161.1960105005327</v>
@@ -3640,7 +3640,7 @@
         <v>171.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>189.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>176.8627394453875</v>
@@ -3656,13 +3656,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>44.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>42.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3701,10 +3701,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>289.5559296952998</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>376.2059480879339</v>
       </c>
       <c r="S40" t="n">
         <v>115.1623649487571</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>96.03989531070653</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3792,16 +3792,16 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>398.0000000000109</v>
+        <v>398.0000000000382</v>
       </c>
       <c r="V41" t="n">
-        <v>398.0000000000097</v>
+        <v>342.2452202167029</v>
       </c>
       <c r="W41" t="n">
-        <v>398.0000000000093</v>
+        <v>398.0000000000359</v>
       </c>
       <c r="X41" t="n">
-        <v>246.2053249060944</v>
+        <v>398.0000000000359</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>263.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3826,16 +3826,16 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>218.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>204.451309459933</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>208.3844268090626</v>
       </c>
       <c r="I42" t="n">
-        <v>86.20280098568816</v>
+        <v>86.20280098568814</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,19 +3862,19 @@
         <v>15.28741603387581</v>
       </c>
       <c r="R42" t="n">
-        <v>398.0000000000148</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>340.2103207193283</v>
+        <v>264.8436372267041</v>
       </c>
       <c r="T42" t="n">
         <v>283.1960105005327</v>
       </c>
       <c r="U42" t="n">
-        <v>279.1913974960358</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>142.4704542645425</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -3947,13 +3947,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>22.5986250264319</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>78.17031021621619</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>100.7689352426481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3978,22 +3978,22 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>85.38916637877857</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>313.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>313.2186788196796</v>
       </c>
       <c r="H44" t="n">
-        <v>311.4927642311656</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>38.31317978318711</v>
+        <v>39.31317978318711</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4029,16 +4029,16 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>398.0000000000111</v>
+        <v>396.0265413971333</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>398.0000000000069</v>
+        <v>398</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>257.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>68.79577803047337</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>249.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>234.451309459933</v>
+        <v>235.451309459933</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>239.3844268090626</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>117.2028009856881</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>45.28741603387581</v>
+        <v>46.28741603387581</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4105,19 +4105,19 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>313.1960105005327</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>309.1913974960358</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>323.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>318.9215993181203</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>329.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>70.38583524264811</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>71.36593524264811</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4324,19 +4324,19 @@
         <v>55.6</v>
       </c>
       <c r="K2" t="n">
-        <v>743.65</v>
+        <v>110.8457870158874</v>
       </c>
       <c r="L2" t="n">
-        <v>1418.413706561317</v>
+        <v>794.3508115402738</v>
       </c>
       <c r="M2" t="n">
-        <v>2021.209946161819</v>
+        <v>1397.147051140776</v>
       </c>
       <c r="N2" t="n">
-        <v>2709.259946161819</v>
+        <v>2085.197051140776</v>
       </c>
       <c r="O2" t="n">
-        <v>2716.012895021043</v>
+        <v>2091.95</v>
       </c>
       <c r="P2" t="n">
         <v>2780</v>
@@ -4348,25 +4348,25 @@
         <v>2780</v>
       </c>
       <c r="S2" t="n">
-        <v>2292.552837964254</v>
+        <v>2696.593242004658</v>
       </c>
       <c r="T2" t="n">
         <v>2106.373594453853</v>
       </c>
       <c r="U2" t="n">
-        <v>1528.240761998562</v>
+        <v>1854.678441856657</v>
       </c>
       <c r="V2" t="n">
-        <v>1296.068010314902</v>
+        <v>1622.505690172997</v>
       </c>
       <c r="W2" t="n">
-        <v>1055.286721445258</v>
+        <v>1381.724401303353</v>
       </c>
       <c r="X2" t="n">
-        <v>861.062647242563</v>
+        <v>1187.500327100658</v>
       </c>
       <c r="Y2" t="n">
-        <v>748.6207960478091</v>
+        <v>1075.058475905904</v>
       </c>
     </row>
     <row r="3">
@@ -4376,16 +4376,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>154.0275969881093</v>
+        <v>750.1191204399794</v>
       </c>
       <c r="C3" t="n">
-        <v>154.0275969881093</v>
+        <v>750.1191204399794</v>
       </c>
       <c r="D3" t="n">
-        <v>55.6</v>
+        <v>398.6669114524009</v>
       </c>
       <c r="E3" t="n">
-        <v>55.6</v>
+        <v>398.6669114524009</v>
       </c>
       <c r="F3" t="n">
         <v>55.6</v>
@@ -4430,22 +4430,22 @@
         <v>1422.401853745313</v>
       </c>
       <c r="T3" t="n">
-        <v>1418.16345930033</v>
+        <v>1221.773612402375</v>
       </c>
       <c r="U3" t="n">
-        <v>1013.92972445585</v>
+        <v>1221.580281598299</v>
       </c>
       <c r="V3" t="n">
-        <v>595.2320808280515</v>
+        <v>802.8826379705007</v>
       </c>
       <c r="W3" t="n">
-        <v>562.5319364746894</v>
+        <v>770.1824936171386</v>
       </c>
       <c r="X3" t="n">
-        <v>542.4685632975302</v>
+        <v>750.1191204399794</v>
       </c>
       <c r="Y3" t="n">
-        <v>542.4685632975302</v>
+        <v>750.1191204399794</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>97.01925870073046</v>
+        <v>2386.166203712219</v>
       </c>
       <c r="C4" t="n">
-        <v>97.01925870073046</v>
+        <v>2386.166203712219</v>
       </c>
       <c r="D4" t="n">
-        <v>97.01925870073046</v>
+        <v>2386.166203712219</v>
       </c>
       <c r="E4" t="n">
-        <v>97.01925870073046</v>
+        <v>2386.166203712219</v>
       </c>
       <c r="F4" t="n">
-        <v>97.01925870073046</v>
+        <v>2386.166203712219</v>
       </c>
       <c r="G4" t="n">
-        <v>250.6650475384354</v>
+        <v>2386.166203712219</v>
       </c>
       <c r="H4" t="n">
-        <v>422.3085422060297</v>
+        <v>2539.419257858151</v>
       </c>
       <c r="I4" t="n">
-        <v>650.6355076994896</v>
+        <v>2767.746223351611</v>
       </c>
       <c r="J4" t="n">
-        <v>680.5700916354413</v>
+        <v>2767.746223351611</v>
       </c>
       <c r="K4" t="n">
-        <v>818.7278829493589</v>
+        <v>2767.746223351611</v>
       </c>
       <c r="L4" t="n">
-        <v>830.9816595977477</v>
+        <v>2780</v>
       </c>
       <c r="M4" t="n">
-        <v>830.9816595977477</v>
+        <v>2780</v>
       </c>
       <c r="N4" t="n">
-        <v>830.9816595977477</v>
+        <v>2780</v>
       </c>
       <c r="O4" t="n">
-        <v>830.9816595977477</v>
+        <v>2780</v>
       </c>
       <c r="P4" t="n">
-        <v>570.1506323246076</v>
+        <v>2519.16897272686</v>
       </c>
       <c r="Q4" t="n">
-        <v>261.4584440159228</v>
+        <v>2210.476784418175</v>
       </c>
       <c r="R4" t="n">
-        <v>55.6</v>
+        <v>2004.61834040226</v>
       </c>
       <c r="S4" t="n">
-        <v>97.01925870073046</v>
+        <v>2046.037599102991</v>
       </c>
       <c r="T4" t="n">
-        <v>97.01925870073046</v>
+        <v>2235.135412688025</v>
       </c>
       <c r="U4" t="n">
-        <v>97.01925870073046</v>
+        <v>2235.135412688025</v>
       </c>
       <c r="V4" t="n">
-        <v>97.01925870073046</v>
+        <v>2235.135412688025</v>
       </c>
       <c r="W4" t="n">
-        <v>97.01925870073046</v>
+        <v>2235.135412688025</v>
       </c>
       <c r="X4" t="n">
-        <v>97.01925870073046</v>
+        <v>2386.166203712219</v>
       </c>
       <c r="Y4" t="n">
-        <v>97.01925870073046</v>
+        <v>2386.166203712219</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>535.1738336854236</v>
+        <v>772.9986695763268</v>
       </c>
       <c r="C5" t="n">
-        <v>485.199512227854</v>
+        <v>318.9839440783531</v>
       </c>
       <c r="D5" t="n">
-        <v>474.7559205714401</v>
+        <v>308.5403524219392</v>
       </c>
       <c r="E5" t="n">
-        <v>470.3485573321788</v>
+        <v>304.132989182678</v>
       </c>
       <c r="F5" t="n">
-        <v>465.4095384351971</v>
+        <v>299.1939702856963</v>
       </c>
       <c r="G5" t="n">
-        <v>462.1583477082481</v>
+        <v>188.7373171862149</v>
       </c>
       <c r="H5" t="n">
-        <v>55.6</v>
+        <v>186.2193735183708</v>
       </c>
       <c r="I5" t="n">
         <v>55.6</v>
@@ -4561,19 +4561,19 @@
         <v>487.0668333479124</v>
       </c>
       <c r="K5" t="n">
-        <v>854.8354783709688</v>
+        <v>542.3126203637997</v>
       </c>
       <c r="L5" t="n">
-        <v>1542.885478370969</v>
+        <v>1230.3626203638</v>
       </c>
       <c r="M5" t="n">
-        <v>1528.915276350767</v>
+        <v>1216.392418343597</v>
       </c>
       <c r="N5" t="n">
-        <v>2216.965276350767</v>
+        <v>1904.442418343597</v>
       </c>
       <c r="O5" t="n">
-        <v>2223.71822520999</v>
+        <v>1911.195367202821</v>
       </c>
       <c r="P5" t="n">
         <v>2287.705330188947</v>
@@ -4585,25 +4585,25 @@
         <v>2560.767782514438</v>
       </c>
       <c r="S5" t="n">
-        <v>2073.320620478692</v>
+        <v>2477.361024519096</v>
       </c>
       <c r="T5" t="n">
-        <v>1649.316541077387</v>
+        <v>2291.181781008695</v>
       </c>
       <c r="U5" t="n">
-        <v>1397.621388480191</v>
+        <v>2039.486628411499</v>
       </c>
       <c r="V5" t="n">
-        <v>1165.448636796531</v>
+        <v>1807.313876727838</v>
       </c>
       <c r="W5" t="n">
-        <v>924.6673479268868</v>
+        <v>1566.532587858194</v>
       </c>
       <c r="X5" t="n">
-        <v>730.4432737241922</v>
+        <v>1372.3085136555</v>
       </c>
       <c r="Y5" t="n">
-        <v>618.0014225294383</v>
+        <v>1259.866662460746</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55.6</v>
+        <v>771.7995952961838</v>
       </c>
       <c r="C6" t="n">
-        <v>55.6</v>
+        <v>407.0522089875785</v>
       </c>
       <c r="D6" t="n">
         <v>55.6</v>
@@ -4658,31 +4658,31 @@
         <v>1614.915790368535</v>
       </c>
       <c r="Q6" t="n">
-        <v>1614.915790368535</v>
+        <v>1477.251733768661</v>
       </c>
       <c r="R6" t="n">
-        <v>1484.230460532513</v>
+        <v>1346.566403932638</v>
       </c>
       <c r="S6" t="n">
-        <v>1422.401853745313</v>
+        <v>1284.737797145438</v>
       </c>
       <c r="T6" t="n">
-        <v>1418.16345930033</v>
+        <v>1280.499402700456</v>
       </c>
       <c r="U6" t="n">
-        <v>1417.970128496254</v>
+        <v>1280.306071896379</v>
       </c>
       <c r="V6" t="n">
-        <v>1403.31288890886</v>
+        <v>1265.648832308985</v>
       </c>
       <c r="W6" t="n">
-        <v>966.5723405150934</v>
+        <v>1232.948687955623</v>
       </c>
       <c r="X6" t="n">
-        <v>542.4685632975302</v>
+        <v>1212.885314778464</v>
       </c>
       <c r="Y6" t="n">
-        <v>139.0429140388086</v>
+        <v>1160.240561605605</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>569.4172912244745</v>
+        <v>519.0072899320008</v>
       </c>
       <c r="C7" t="n">
-        <v>569.4172912244745</v>
+        <v>519.0072899320008</v>
       </c>
       <c r="D7" t="n">
-        <v>569.4172912244745</v>
+        <v>632.3264340570009</v>
       </c>
       <c r="E7" t="n">
-        <v>569.4172912244745</v>
+        <v>632.3264340570009</v>
       </c>
       <c r="F7" t="n">
-        <v>569.4172912244745</v>
+        <v>756.6874066489364</v>
       </c>
       <c r="G7" t="n">
-        <v>723.0630800621794</v>
+        <v>756.6874066489364</v>
       </c>
       <c r="H7" t="n">
-        <v>723.0630800621794</v>
+        <v>756.6874066489364</v>
       </c>
       <c r="I7" t="n">
-        <v>723.0630800621794</v>
+        <v>756.6874066489364</v>
       </c>
       <c r="J7" t="n">
-        <v>818.7278829493603</v>
+        <v>756.6874066489364</v>
       </c>
       <c r="K7" t="n">
-        <v>818.7278829493603</v>
+        <v>818.7278829493667</v>
       </c>
       <c r="L7" t="n">
-        <v>830.9816595977491</v>
+        <v>830.9816595977555</v>
       </c>
       <c r="M7" t="n">
-        <v>830.9816595977491</v>
+        <v>830.9816595977555</v>
       </c>
       <c r="N7" t="n">
-        <v>830.9816595977491</v>
+        <v>830.9816595977555</v>
       </c>
       <c r="O7" t="n">
-        <v>830.9816595977491</v>
+        <v>830.9816595977555</v>
       </c>
       <c r="P7" t="n">
-        <v>570.150632324609</v>
+        <v>570.1506323246155</v>
       </c>
       <c r="Q7" t="n">
-        <v>261.4584440159241</v>
+        <v>261.4584440159306</v>
       </c>
       <c r="R7" t="n">
         <v>55.6</v>
@@ -4746,22 +4746,22 @@
         <v>97.01925870073049</v>
       </c>
       <c r="T7" t="n">
-        <v>286.1170722857648</v>
+        <v>97.01925870073049</v>
       </c>
       <c r="U7" t="n">
-        <v>286.1170722857648</v>
+        <v>97.01925870073049</v>
       </c>
       <c r="V7" t="n">
-        <v>286.1170722857648</v>
+        <v>295.8406515866765</v>
       </c>
       <c r="W7" t="n">
-        <v>458.0079905454422</v>
+        <v>295.8406515866765</v>
       </c>
       <c r="X7" t="n">
-        <v>458.0079905454422</v>
+        <v>295.8406515866765</v>
       </c>
       <c r="Y7" t="n">
-        <v>569.4172912244745</v>
+        <v>407.2499522657087</v>
       </c>
     </row>
     <row r="8">
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1069.833611244199</v>
+        <v>665.7932072037945</v>
       </c>
       <c r="C8" t="n">
-        <v>1019.859289786629</v>
+        <v>615.8188857462249</v>
       </c>
       <c r="D8" t="n">
         <v>605.375294089811</v>
@@ -4786,7 +4786,7 @@
         <v>596.028911953568</v>
       </c>
       <c r="G8" t="n">
-        <v>592.777721226619</v>
+        <v>188.7373171862149</v>
       </c>
       <c r="H8" t="n">
         <v>186.2193735183708</v>
@@ -4795,25 +4795,25 @@
         <v>55.6</v>
       </c>
       <c r="J8" t="n">
-        <v>55.6</v>
+        <v>487.0668333479124</v>
       </c>
       <c r="K8" t="n">
-        <v>110.8457870158874</v>
+        <v>1175.116833347912</v>
       </c>
       <c r="L8" t="n">
-        <v>302.0561417292211</v>
+        <v>1247.015186223401</v>
       </c>
       <c r="M8" t="n">
-        <v>904.8523813297236</v>
+        <v>1849.811425823903</v>
       </c>
       <c r="N8" t="n">
-        <v>1592.902381329724</v>
+        <v>2537.861425823903</v>
       </c>
       <c r="O8" t="n">
-        <v>1599.655330188947</v>
+        <v>2544.614374683127</v>
       </c>
       <c r="P8" t="n">
-        <v>2287.705330188947</v>
+        <v>2608.601479662084</v>
       </c>
       <c r="Q8" t="n">
         <v>2780</v>
@@ -4825,22 +4825,22 @@
         <v>2477.361024519096</v>
       </c>
       <c r="T8" t="n">
-        <v>2183.976318636162</v>
+        <v>1887.141376968291</v>
       </c>
       <c r="U8" t="n">
-        <v>1932.281166038967</v>
+        <v>1528.240761998562</v>
       </c>
       <c r="V8" t="n">
-        <v>1700.108414355306</v>
+        <v>1296.068010314902</v>
       </c>
       <c r="W8" t="n">
-        <v>1459.327125485662</v>
+        <v>1055.286721445258</v>
       </c>
       <c r="X8" t="n">
-        <v>1265.103051282967</v>
+        <v>861.062647242563</v>
       </c>
       <c r="Y8" t="n">
-        <v>1152.661200088213</v>
+        <v>748.6207960478091</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>962.1084050689174</v>
+        <v>750.1191204399794</v>
       </c>
       <c r="C9" t="n">
-        <v>735.7909054117532</v>
+        <v>750.1191204399794</v>
       </c>
       <c r="D9" t="n">
-        <v>384.3386964241748</v>
+        <v>398.6669114524009</v>
       </c>
       <c r="E9" t="n">
-        <v>384.3386964241748</v>
+        <v>398.6669114524009</v>
       </c>
       <c r="F9" t="n">
-        <v>384.3386964241748</v>
+        <v>55.6</v>
       </c>
       <c r="G9" t="n">
         <v>55.6</v>
@@ -4895,31 +4895,31 @@
         <v>1614.915790368535</v>
       </c>
       <c r="Q9" t="n">
-        <v>1614.915790368535</v>
+        <v>1477.251733768661</v>
       </c>
       <c r="R9" t="n">
-        <v>1484.230460532513</v>
+        <v>1346.566403932638</v>
       </c>
       <c r="S9" t="n">
-        <v>1422.401853745313</v>
+        <v>1284.737797145438</v>
       </c>
       <c r="T9" t="n">
-        <v>1418.16345930033</v>
+        <v>1280.499402700456</v>
       </c>
       <c r="U9" t="n">
-        <v>1417.970128496254</v>
+        <v>1280.306071896379</v>
       </c>
       <c r="V9" t="n">
-        <v>1403.31288890886</v>
+        <v>1265.648832308985</v>
       </c>
       <c r="W9" t="n">
-        <v>1370.612744555497</v>
+        <v>1232.948687955623</v>
       </c>
       <c r="X9" t="n">
-        <v>1350.549371378338</v>
+        <v>808.8449107380595</v>
       </c>
       <c r="Y9" t="n">
-        <v>1350.549371378338</v>
+        <v>750.1191204399794</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>830.9816595977391</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="C10" t="n">
-        <v>830.9816595977391</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="D10" t="n">
-        <v>830.9816595977391</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="E10" t="n">
-        <v>830.9816595977391</v>
+        <v>403.9459764971779</v>
       </c>
       <c r="F10" t="n">
-        <v>830.9816595977391</v>
+        <v>403.9459764971779</v>
       </c>
       <c r="G10" t="n">
-        <v>830.9816595977391</v>
+        <v>403.9459764971779</v>
       </c>
       <c r="H10" t="n">
-        <v>830.9816595977391</v>
+        <v>403.9459764971779</v>
       </c>
       <c r="I10" t="n">
-        <v>830.9816595977391</v>
+        <v>403.9459764971779</v>
       </c>
       <c r="J10" t="n">
-        <v>830.9816595977391</v>
+        <v>680.5700916354369</v>
       </c>
       <c r="K10" t="n">
-        <v>830.9816595977391</v>
+        <v>818.7278829493546</v>
       </c>
       <c r="L10" t="n">
-        <v>830.9816595977391</v>
+        <v>830.9816595977434</v>
       </c>
       <c r="M10" t="n">
-        <v>830.9816595977391</v>
+        <v>747.3922193666531</v>
       </c>
       <c r="N10" t="n">
-        <v>830.9816595977391</v>
+        <v>611.8289209468355</v>
       </c>
       <c r="O10" t="n">
-        <v>625.1232155818249</v>
+        <v>403.4542329385574</v>
       </c>
       <c r="P10" t="n">
-        <v>364.2921883086848</v>
+        <v>374.5264084591855</v>
       </c>
       <c r="Q10" t="n">
-        <v>55.6</v>
+        <v>374.5264084591855</v>
       </c>
       <c r="R10" t="n">
         <v>55.6</v>
       </c>
       <c r="S10" t="n">
-        <v>55.6</v>
+        <v>97.01925870073046</v>
       </c>
       <c r="T10" t="n">
-        <v>213.7051072892388</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="U10" t="n">
-        <v>460.2693484521157</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="V10" t="n">
-        <v>659.0907413380617</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="W10" t="n">
-        <v>830.9816595977391</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="X10" t="n">
-        <v>830.9816595977391</v>
+        <v>286.1170722857648</v>
       </c>
       <c r="Y10" t="n">
-        <v>830.9816595977391</v>
+        <v>286.1170722857648</v>
       </c>
     </row>
     <row r="11">
@@ -5008,16 +5008,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1070.638855192482</v>
+        <v>1264.466762978353</v>
       </c>
       <c r="C11" t="n">
-        <v>831.7756448460239</v>
+        <v>1025.603552631894</v>
       </c>
       <c r="D11" t="n">
-        <v>632.443164300721</v>
+        <v>826.2710720865916</v>
       </c>
       <c r="E11" t="n">
-        <v>439.1469121725709</v>
+        <v>632.9748199584415</v>
       </c>
       <c r="F11" t="n">
         <v>439.1469121725709</v>
@@ -5062,22 +5062,22 @@
         <v>2503.623650781722</v>
       </c>
       <c r="T11" t="n">
-        <v>2166.052337503054</v>
+        <v>2128.555518382432</v>
       </c>
       <c r="U11" t="n">
-        <v>1725.46829601697</v>
+        <v>2128.555518382432</v>
       </c>
       <c r="V11" t="n">
-        <v>1725.46829601697</v>
+        <v>2128.555518382432</v>
       </c>
       <c r="W11" t="n">
-        <v>1725.46829601697</v>
+        <v>2128.555518382432</v>
       </c>
       <c r="X11" t="n">
-        <v>1342.355332925386</v>
+        <v>1837.513980794899</v>
       </c>
       <c r="Y11" t="n">
-        <v>1342.355332925386</v>
+        <v>1536.183240711257</v>
       </c>
     </row>
     <row r="12">
@@ -5111,22 +5111,22 @@
         <v>61.33922702416873</v>
       </c>
       <c r="J12" t="n">
-        <v>212.2545119164488</v>
+        <v>423.1245119164489</v>
       </c>
       <c r="K12" t="n">
-        <v>658.3941508410209</v>
+        <v>869.2641508410209</v>
       </c>
       <c r="L12" t="n">
-        <v>1202.570586964523</v>
+        <v>1413.440586964523</v>
       </c>
       <c r="M12" t="n">
-        <v>1571.820828707382</v>
+        <v>1600.563665698077</v>
       </c>
       <c r="N12" t="n">
-        <v>1990.184371239479</v>
+        <v>2018.927208230174</v>
       </c>
       <c r="O12" t="n">
-        <v>2325.860292178043</v>
+        <v>2536.730292178043</v>
       </c>
       <c r="P12" t="n">
         <v>2703.747854383399</v>
@@ -5178,34 +5178,34 @@
         <v>121.1855589078878</v>
       </c>
       <c r="F13" t="n">
-        <v>105.7748963703047</v>
+        <v>121.1855589078878</v>
       </c>
       <c r="G13" t="n">
-        <v>105.7748963703047</v>
+        <v>121.1855589078878</v>
       </c>
       <c r="H13" t="n">
-        <v>92.01456035111717</v>
+        <v>107.4252228887002</v>
       </c>
       <c r="I13" t="n">
-        <v>135.2115258445771</v>
+        <v>150.6221883821602</v>
       </c>
       <c r="J13" t="n">
-        <v>328.0783291199792</v>
+        <v>343.4889916575623</v>
       </c>
       <c r="K13" t="n">
-        <v>328.0783291199792</v>
+        <v>343.4889916575623</v>
       </c>
       <c r="L13" t="n">
-        <v>328.0783291199792</v>
+        <v>343.4889916575623</v>
       </c>
       <c r="M13" t="n">
-        <v>55.6</v>
+        <v>343.4889916575623</v>
       </c>
       <c r="N13" t="n">
-        <v>55.6</v>
+        <v>343.4889916575623</v>
       </c>
       <c r="O13" t="n">
-        <v>55.6</v>
+        <v>343.4889916575623</v>
       </c>
       <c r="P13" t="n">
         <v>55.6</v>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55.6</v>
+        <v>303.626678436301</v>
       </c>
       <c r="C14" t="n">
-        <v>55.6</v>
+        <v>69.81397314034754</v>
       </c>
       <c r="D14" t="n">
         <v>55.6</v>
@@ -5269,52 +5269,52 @@
         <v>55.6</v>
       </c>
       <c r="J14" t="n">
-        <v>492.1728383642889</v>
+        <v>66.17114914399374</v>
       </c>
       <c r="K14" t="n">
-        <v>1180.222838364289</v>
+        <v>754.2211491439938</v>
       </c>
       <c r="L14" t="n">
-        <v>1264.382609017555</v>
+        <v>894.5502929189333</v>
       </c>
       <c r="M14" t="n">
-        <v>1868.875398450008</v>
+        <v>1499.043082351386</v>
       </c>
       <c r="N14" t="n">
-        <v>2556.925398450008</v>
+        <v>2187.093082351386</v>
       </c>
       <c r="O14" t="n">
-        <v>2577.236158626933</v>
+        <v>2207.403842528311</v>
       </c>
       <c r="P14" t="n">
-        <v>2653.642115216809</v>
+        <v>2283.809799118187</v>
       </c>
       <c r="Q14" t="n">
         <v>2780</v>
       </c>
       <c r="R14" t="n">
-        <v>2779.959701706357</v>
+        <v>2780</v>
       </c>
       <c r="S14" t="n">
-        <v>2649.861344841759</v>
+        <v>2512.754858166275</v>
       </c>
       <c r="T14" t="n">
-        <v>2278.833616482872</v>
+        <v>2142.737230817489</v>
       </c>
       <c r="U14" t="n">
-        <v>1842.289979037192</v>
+        <v>1707.203694381909</v>
       </c>
       <c r="V14" t="n">
-        <v>1425.268742505047</v>
+        <v>1291.192558859865</v>
       </c>
       <c r="W14" t="n">
-        <v>999.6389687869178</v>
+        <v>866.5728861518373</v>
       </c>
       <c r="X14" t="n">
-        <v>620.5664097357383</v>
+        <v>866.5728861518373</v>
       </c>
       <c r="Y14" t="n">
-        <v>323.2760736924996</v>
+        <v>570.2926511186995</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>807.2986617899062</v>
+        <v>801.2380557293</v>
       </c>
       <c r="C15" t="n">
-        <v>661.74319467322</v>
+        <v>656.6926896227149</v>
       </c>
       <c r="D15" t="n">
-        <v>529.4829048775608</v>
+        <v>525.4425008371567</v>
       </c>
       <c r="E15" t="n">
-        <v>402.5413925321945</v>
+        <v>399.5110895018914</v>
       </c>
       <c r="F15" t="n">
-        <v>278.6664002717128</v>
+        <v>276.6461982515108</v>
       </c>
       <c r="G15" t="n">
-        <v>169.1196230394572</v>
+        <v>168.1095220293562</v>
       </c>
       <c r="H15" t="n">
         <v>55.6</v>
       </c>
       <c r="I15" t="n">
-        <v>65.29922702416873</v>
+        <v>66.28922702416872</v>
       </c>
       <c r="J15" t="n">
-        <v>431.0445119164489</v>
+        <v>433.0245119164488</v>
       </c>
       <c r="K15" t="n">
-        <v>666.3141508410209</v>
+        <v>884.114150841021</v>
       </c>
       <c r="L15" t="n">
-        <v>999.620586964523</v>
+        <v>1351.575848197642</v>
       </c>
       <c r="M15" t="n">
-        <v>1313.247605092016</v>
+        <v>1725.776089940501</v>
       </c>
       <c r="N15" t="n">
-        <v>1735.571147624113</v>
+        <v>1933.269632472598</v>
       </c>
       <c r="O15" t="n">
-        <v>2257.334231571982</v>
+        <v>2240.202716420467</v>
       </c>
       <c r="P15" t="n">
-        <v>2639.181793777338</v>
+        <v>2623.040278625823</v>
       </c>
       <c r="Q15" t="n">
-        <v>2719.087251903801</v>
+        <v>2703.935736752286</v>
       </c>
       <c r="R15" t="n">
-        <v>2403.553437219294</v>
+        <v>2389.41202307788</v>
       </c>
       <c r="S15" t="n">
-        <v>2156.876345583609</v>
+        <v>2143.745032452296</v>
       </c>
       <c r="T15" t="n">
-        <v>1967.789466290141</v>
+        <v>1955.668254168929</v>
       </c>
       <c r="U15" t="n">
-        <v>1782.74765063758</v>
+        <v>1771.636539526469</v>
       </c>
       <c r="V15" t="n">
-        <v>1583.241926201701</v>
+        <v>1573.140916100691</v>
       </c>
       <c r="W15" t="n">
-        <v>1365.693296999854</v>
+        <v>1356.602387908945</v>
       </c>
       <c r="X15" t="n">
-        <v>1160.78143897421</v>
+        <v>1152.700630893402</v>
       </c>
       <c r="Y15" t="n">
-        <v>976.5477089074078</v>
+        <v>969.4770018367005</v>
       </c>
     </row>
     <row r="16">
@@ -5403,49 +5403,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="C16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="D16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="E16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="F16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="G16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="H16" t="n">
-        <v>127.3860309695083</v>
+        <v>132.3762329897103</v>
       </c>
       <c r="I16" t="n">
-        <v>174.5429964629682</v>
+        <v>180.5231984831703</v>
       </c>
       <c r="J16" t="n">
-        <v>371.3697997383704</v>
+        <v>378.3400017585724</v>
       </c>
       <c r="K16" t="n">
-        <v>371.3697997383704</v>
+        <v>378.3400017585724</v>
       </c>
       <c r="L16" t="n">
-        <v>371.3697997383704</v>
+        <v>378.3400017585724</v>
       </c>
       <c r="M16" t="n">
-        <v>371.3697997383704</v>
+        <v>378.3400017585724</v>
       </c>
       <c r="N16" t="n">
-        <v>371.3697997383704</v>
+        <v>378.3400017585724</v>
       </c>
       <c r="O16" t="n">
-        <v>371.3697997383704</v>
+        <v>378.3400017585724</v>
       </c>
       <c r="P16" t="n">
-        <v>371.3697997383704</v>
+        <v>378.3400017585724</v>
       </c>
       <c r="Q16" t="n">
         <v>55.6</v>
@@ -5457,22 +5457,22 @@
         <v>55.6</v>
       </c>
       <c r="T16" t="n">
-        <v>63.52781358503437</v>
+        <v>64.51781358503438</v>
       </c>
       <c r="U16" t="n">
-        <v>128.9220547479112</v>
+        <v>130.9020547479112</v>
       </c>
       <c r="V16" t="n">
-        <v>146.5734476338571</v>
+        <v>149.5434476338571</v>
       </c>
       <c r="W16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="X16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
       <c r="Y16" t="n">
-        <v>137.1059629482918</v>
+        <v>141.0860639583928</v>
       </c>
     </row>
     <row r="17">
@@ -5482,13 +5482,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>652.8369476679499</v>
+        <v>688.709187220777</v>
       </c>
       <c r="C17" t="n">
-        <v>509.9333332810873</v>
+        <v>545.8055728339145</v>
       </c>
       <c r="D17" t="n">
-        <v>406.5604486953804</v>
+        <v>442.4326882482077</v>
       </c>
       <c r="E17" t="n">
         <v>345.0960320796535</v>
@@ -5506,25 +5506,25 @@
         <v>55.6</v>
       </c>
       <c r="J17" t="n">
-        <v>122.340522265667</v>
+        <v>492.1728383642889</v>
       </c>
       <c r="K17" t="n">
-        <v>810.390522265667</v>
+        <v>1180.222838364289</v>
       </c>
       <c r="L17" t="n">
-        <v>894.5502929189333</v>
+        <v>1264.382609017555</v>
       </c>
       <c r="M17" t="n">
-        <v>1499.043082351386</v>
+        <v>1868.875398450008</v>
       </c>
       <c r="N17" t="n">
-        <v>2187.093082351386</v>
+        <v>2556.925398450008</v>
       </c>
       <c r="O17" t="n">
-        <v>2207.403842528311</v>
+        <v>2577.236158626933</v>
       </c>
       <c r="P17" t="n">
-        <v>2283.809799118187</v>
+        <v>2653.642115216809</v>
       </c>
       <c r="Q17" t="n">
         <v>2780</v>
@@ -5542,16 +5542,16 @@
         <v>1979.930967109182</v>
       </c>
       <c r="V17" t="n">
-        <v>1654.828922496229</v>
+        <v>1690.701162049056</v>
       </c>
       <c r="W17" t="n">
-        <v>1321.118340697292</v>
+        <v>1356.990580250119</v>
       </c>
       <c r="X17" t="n">
-        <v>1033.964973565304</v>
+        <v>1069.837213118132</v>
       </c>
       <c r="Y17" t="n">
-        <v>828.5938294412574</v>
+        <v>864.4660689940846</v>
       </c>
     </row>
     <row r="18">
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>255.7835102747546</v>
+        <v>530.3999275273676</v>
       </c>
       <c r="C18" t="n">
         <v>202.1472350772604</v>
@@ -5612,25 +5612,25 @@
         <v>1391.30116760322</v>
       </c>
       <c r="S18" t="n">
-        <v>961.926850634114</v>
+        <v>1236.543267886727</v>
       </c>
       <c r="T18" t="n">
-        <v>864.7591632598385</v>
+        <v>1139.375580512451</v>
       </c>
       <c r="U18" t="n">
-        <v>771.6365395264689</v>
+        <v>1046.252956779082</v>
       </c>
       <c r="V18" t="n">
-        <v>664.0500070097819</v>
+        <v>938.6664242623948</v>
       </c>
       <c r="W18" t="n">
-        <v>538.4205697271268</v>
+        <v>813.0369869797397</v>
       </c>
       <c r="X18" t="n">
-        <v>425.4279036206748</v>
+        <v>700.0443208732877</v>
       </c>
       <c r="Y18" t="n">
-        <v>333.1133654730643</v>
+        <v>607.7297827256773</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1330.173665597915</v>
       </c>
       <c r="L19" t="n">
-        <v>1330.173665597915</v>
+        <v>1249.746950618208</v>
       </c>
       <c r="M19" t="n">
-        <v>1330.173665597915</v>
+        <v>1073.228217457825</v>
       </c>
       <c r="N19" t="n">
-        <v>1330.173665597915</v>
+        <v>844.7356261087145</v>
       </c>
       <c r="O19" t="n">
-        <v>1222.837502828889</v>
+        <v>543.4316451711435</v>
       </c>
       <c r="P19" t="n">
-        <v>869.0771826264563</v>
+        <v>189.6713249687105</v>
       </c>
       <c r="Q19" t="n">
-        <v>467.4557013884785</v>
+        <v>189.6713249687105</v>
       </c>
       <c r="R19" t="n">
-        <v>55.6</v>
+        <v>106.269055503795</v>
       </c>
       <c r="S19" t="n">
         <v>55.6</v>
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>652.8369476679499</v>
+        <v>688.709187220777</v>
       </c>
       <c r="C20" t="n">
-        <v>509.9333332810873</v>
+        <v>545.8055728339145</v>
       </c>
       <c r="D20" t="n">
         <v>442.4326882482077</v>
@@ -5743,25 +5743,25 @@
         <v>55.6</v>
       </c>
       <c r="J20" t="n">
-        <v>66.17114914399374</v>
+        <v>492.1728383642889</v>
       </c>
       <c r="K20" t="n">
-        <v>754.2211491439938</v>
+        <v>1180.222838364289</v>
       </c>
       <c r="L20" t="n">
-        <v>1442.271149143994</v>
+        <v>1390.740493800747</v>
       </c>
       <c r="M20" t="n">
-        <v>2046.763938576446</v>
+        <v>1995.233283233199</v>
       </c>
       <c r="N20" t="n">
-        <v>2046.763938576446</v>
+        <v>2683.283283233199</v>
       </c>
       <c r="O20" t="n">
-        <v>2067.074698753371</v>
+        <v>2703.594043410124</v>
       </c>
       <c r="P20" t="n">
-        <v>2755.124698753371</v>
+        <v>2780</v>
       </c>
       <c r="Q20" t="n">
         <v>2780</v>
@@ -5782,13 +5782,13 @@
         <v>1654.828922496229</v>
       </c>
       <c r="W20" t="n">
-        <v>1321.118340697292</v>
+        <v>1356.990580250119</v>
       </c>
       <c r="X20" t="n">
-        <v>1033.964973565304</v>
+        <v>1069.837213118132</v>
       </c>
       <c r="Y20" t="n">
-        <v>828.5938294412574</v>
+        <v>864.4660689940846</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>392.7358709274927</v>
+        <v>255.7835102747546</v>
       </c>
       <c r="C21" t="n">
-        <v>339.0995957299985</v>
+        <v>202.1472350772604</v>
       </c>
       <c r="D21" t="n">
-        <v>298.7584978535312</v>
+        <v>161.8061372007931</v>
       </c>
       <c r="E21" t="n">
-        <v>263.7361774273568</v>
+        <v>126.7838167746187</v>
       </c>
       <c r="F21" t="n">
         <v>94.82801643332894</v>
@@ -5843,31 +5843,31 @@
         <v>1614.915790368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>1477.251733768661</v>
+        <v>1614.915790368535</v>
       </c>
       <c r="R21" t="n">
-        <v>1253.637111003345</v>
+        <v>1391.30116760322</v>
       </c>
       <c r="S21" t="n">
-        <v>1098.879211286852</v>
+        <v>1236.543267886727</v>
       </c>
       <c r="T21" t="n">
-        <v>1001.711523912577</v>
+        <v>864.7591632598385</v>
       </c>
       <c r="U21" t="n">
-        <v>908.588900179207</v>
+        <v>771.6365395264689</v>
       </c>
       <c r="V21" t="n">
-        <v>801.00236766252</v>
+        <v>664.0500070097819</v>
       </c>
       <c r="W21" t="n">
-        <v>675.3729303798649</v>
+        <v>538.4205697271268</v>
       </c>
       <c r="X21" t="n">
-        <v>562.3802642734129</v>
+        <v>425.4279036206748</v>
       </c>
       <c r="Y21" t="n">
-        <v>470.0657261258024</v>
+        <v>333.1133654730643</v>
       </c>
     </row>
     <row r="22">
@@ -5910,19 +5910,19 @@
         <v>1330.173665597915</v>
       </c>
       <c r="M22" t="n">
-        <v>1153.654932437532</v>
+        <v>1330.173665597915</v>
       </c>
       <c r="N22" t="n">
-        <v>925.162341088422</v>
+        <v>1330.173665597915</v>
       </c>
       <c r="O22" t="n">
-        <v>925.162341088422</v>
+        <v>1028.869684660344</v>
       </c>
       <c r="P22" t="n">
-        <v>571.402020885989</v>
+        <v>869.0771826264563</v>
       </c>
       <c r="Q22" t="n">
-        <v>169.7805396480112</v>
+        <v>467.4557013884785</v>
       </c>
       <c r="R22" t="n">
         <v>55.6</v>
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>689.4291872207771</v>
+        <v>672.8369476679499</v>
       </c>
       <c r="C23" t="n">
-        <v>546.5255728339146</v>
+        <v>529.9333332810872</v>
       </c>
       <c r="D23" t="n">
-        <v>443.1526882482077</v>
+        <v>426.5604486953804</v>
       </c>
       <c r="E23" t="n">
-        <v>345.8160320796535</v>
+        <v>329.2237925268262</v>
       </c>
       <c r="F23" t="n">
-        <v>247.9477202533789</v>
+        <v>231.3554807005516</v>
       </c>
       <c r="G23" t="n">
-        <v>151.767236597137</v>
+        <v>151.447236597137</v>
       </c>
       <c r="H23" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="I23" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="J23" t="n">
-        <v>492.8928383642889</v>
+        <v>492.5728383642889</v>
       </c>
       <c r="K23" t="n">
-        <v>560.7314292185603</v>
+        <v>1185.572838364289</v>
       </c>
       <c r="L23" t="n">
-        <v>1257.69142921856</v>
+        <v>1405.790493800747</v>
       </c>
       <c r="M23" t="n">
-        <v>1862.184218651013</v>
+        <v>2010.283283233199</v>
       </c>
       <c r="N23" t="n">
-        <v>2559.144218651013</v>
+        <v>2703.283283233199</v>
       </c>
       <c r="O23" t="n">
-        <v>2579.454978827938</v>
+        <v>2723.594043410124</v>
       </c>
       <c r="P23" t="n">
-        <v>2655.860935417814</v>
+        <v>2800</v>
       </c>
       <c r="Q23" t="n">
-        <v>2816</v>
+        <v>2800</v>
       </c>
       <c r="R23" t="n">
-        <v>2816</v>
+        <v>2800</v>
       </c>
       <c r="S23" t="n">
-        <v>2640.256188628192</v>
+        <v>2623.663949075366</v>
       </c>
       <c r="T23" t="n">
-        <v>2361.147652188498</v>
+        <v>2344.555412635671</v>
       </c>
       <c r="U23" t="n">
-        <v>2016.523206662009</v>
+        <v>1999.930967109182</v>
       </c>
       <c r="V23" t="n">
-        <v>1691.421162049056</v>
+        <v>1674.828922496229</v>
       </c>
       <c r="W23" t="n">
-        <v>1357.710580250119</v>
+        <v>1341.118340697292</v>
       </c>
       <c r="X23" t="n">
-        <v>1070.557213118132</v>
+        <v>1053.964973565304</v>
       </c>
       <c r="Y23" t="n">
-        <v>865.1860689940846</v>
+        <v>848.5938294412574</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>256.5035102747546</v>
+        <v>530.7999275273677</v>
       </c>
       <c r="C24" t="n">
-        <v>202.8672350772604</v>
+        <v>477.1636523298735</v>
       </c>
       <c r="D24" t="n">
-        <v>162.5261372007931</v>
+        <v>436.8225544534062</v>
       </c>
       <c r="E24" t="n">
-        <v>127.5038167746187</v>
+        <v>127.1838167746187</v>
       </c>
       <c r="F24" t="n">
-        <v>95.54801643332894</v>
+        <v>95.2280164333289</v>
       </c>
       <c r="G24" t="n">
-        <v>77.92043112026529</v>
+        <v>77.60043112026528</v>
       </c>
       <c r="H24" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="I24" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="J24" t="n">
-        <v>207.2352848922801</v>
+        <v>206.9152848922801</v>
       </c>
       <c r="K24" t="n">
-        <v>442.5049238168522</v>
+        <v>442.1849238168522</v>
       </c>
       <c r="L24" t="n">
-        <v>775.8113599403541</v>
+        <v>775.4913599403542</v>
       </c>
       <c r="M24" t="n">
-        <v>934.1916016832133</v>
+        <v>933.8716016832134</v>
       </c>
       <c r="N24" t="n">
-        <v>1141.68514421531</v>
+        <v>1141.36514421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1448.61822816318</v>
+        <v>1448.29822816318</v>
       </c>
       <c r="P24" t="n">
-        <v>1615.635790368535</v>
+        <v>1615.315790368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1615.635790368535</v>
+        <v>1615.315790368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1392.02116760322</v>
+        <v>1391.70116760322</v>
       </c>
       <c r="S24" t="n">
-        <v>1237.263267886727</v>
+        <v>1236.943267886727</v>
       </c>
       <c r="T24" t="n">
-        <v>1140.095580512451</v>
+        <v>1139.775580512451</v>
       </c>
       <c r="U24" t="n">
-        <v>1046.972956779082</v>
+        <v>1046.652956779082</v>
       </c>
       <c r="V24" t="n">
-        <v>939.3864242623948</v>
+        <v>939.0664242623949</v>
       </c>
       <c r="W24" t="n">
-        <v>813.7569869797397</v>
+        <v>813.4369869797398</v>
       </c>
       <c r="X24" t="n">
-        <v>426.1479036206748</v>
+        <v>700.4443208732878</v>
       </c>
       <c r="Y24" t="n">
-        <v>333.8333654730643</v>
+        <v>608.1297827256774</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>599.3317952630525</v>
+        <v>599.0117952630525</v>
       </c>
       <c r="C25" t="n">
-        <v>634.2538010814883</v>
+        <v>633.9338010814882</v>
       </c>
       <c r="D25" t="n">
-        <v>656.4929452064883</v>
+        <v>656.1729452064883</v>
       </c>
       <c r="E25" t="n">
-        <v>683.2418494179013</v>
+        <v>682.9218494179013</v>
       </c>
       <c r="F25" t="n">
-        <v>716.5228220098368</v>
+        <v>716.2028220098367</v>
       </c>
       <c r="G25" t="n">
-        <v>779.0886108475418</v>
+        <v>778.7686108475417</v>
       </c>
       <c r="H25" t="n">
-        <v>859.6521055151361</v>
+        <v>859.332105515136</v>
       </c>
       <c r="I25" t="n">
-        <v>996.899071008596</v>
+        <v>996.579071008596</v>
       </c>
       <c r="J25" t="n">
-        <v>1283.815874283998</v>
+        <v>1283.495874283998</v>
       </c>
       <c r="K25" t="n">
-        <v>1330.893665597916</v>
+        <v>1330.573665597916</v>
       </c>
       <c r="L25" t="n">
-        <v>1330.893665597916</v>
+        <v>1330.573665597916</v>
       </c>
       <c r="M25" t="n">
-        <v>1154.374932437533</v>
+        <v>1330.573665597916</v>
       </c>
       <c r="N25" t="n">
-        <v>925.8823410884222</v>
+        <v>1330.573665597916</v>
       </c>
       <c r="O25" t="n">
-        <v>624.5783601508512</v>
+        <v>1223.237502828889</v>
       </c>
       <c r="P25" t="n">
-        <v>270.8180399484182</v>
+        <v>869.4771826264562</v>
       </c>
       <c r="Q25" t="n">
-        <v>56.32</v>
+        <v>467.8557013884785</v>
       </c>
       <c r="R25" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="S25" t="n">
-        <v>56.32</v>
+        <v>56</v>
       </c>
       <c r="T25" t="n">
-        <v>154.3378135850344</v>
+        <v>154.0178135850344</v>
       </c>
       <c r="U25" t="n">
-        <v>309.8220547479112</v>
+        <v>309.5020547479112</v>
       </c>
       <c r="V25" t="n">
-        <v>417.5634476338572</v>
+        <v>417.2434476338572</v>
       </c>
       <c r="W25" t="n">
-        <v>498.3743658935346</v>
+        <v>498.0543658935346</v>
       </c>
       <c r="X25" t="n">
-        <v>558.3251569177281</v>
+        <v>558.0051569177281</v>
       </c>
       <c r="Y25" t="n">
-        <v>578.6544575967604</v>
+        <v>578.3344575967603</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>414.4985050212281</v>
+        <v>31.84</v>
       </c>
       <c r="C26" t="n">
-        <v>414.4985050212281</v>
+        <v>31.84</v>
       </c>
       <c r="D26" t="n">
-        <v>219.2064285163293</v>
+        <v>31.84</v>
       </c>
       <c r="E26" t="n">
-        <v>219.2064285163293</v>
+        <v>31.84</v>
       </c>
       <c r="F26" t="n">
-        <v>219.2064285163293</v>
+        <v>31.84</v>
       </c>
       <c r="G26" t="n">
-        <v>219.2064285163293</v>
+        <v>31.84</v>
       </c>
       <c r="H26" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I26" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J26" t="n">
-        <v>425.8600000000061</v>
+        <v>425.8600000000114</v>
       </c>
       <c r="K26" t="n">
-        <v>493.6985908542775</v>
+        <v>493.6985908542828</v>
       </c>
       <c r="L26" t="n">
-        <v>577.8583615075438</v>
+        <v>707.2432832331764</v>
       </c>
       <c r="M26" t="n">
-        <v>971.8783615075495</v>
+        <v>1101.263283233188</v>
       </c>
       <c r="N26" t="n">
-        <v>1101.263283233212</v>
+        <v>1495.283283233199</v>
       </c>
       <c r="O26" t="n">
-        <v>1121.574043410137</v>
+        <v>1515.594043410124</v>
       </c>
       <c r="P26" t="n">
-        <v>1197.980000000013</v>
+        <v>1592</v>
       </c>
       <c r="Q26" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R26" t="n">
-        <v>1591.959701706376</v>
+        <v>1591.959701706357</v>
       </c>
       <c r="S26" t="n">
-        <v>1323.704458862549</v>
+        <v>1323.70445886253</v>
       </c>
       <c r="T26" t="n">
-        <v>952.6767305036626</v>
+        <v>952.676730503644</v>
       </c>
       <c r="U26" t="n">
-        <v>952.6767305036626</v>
+        <v>952.676730503644</v>
       </c>
       <c r="V26" t="n">
-        <v>550.6565284834526</v>
+        <v>731.1505380634721</v>
       </c>
       <c r="W26" t="n">
-        <v>414.4985050212281</v>
+        <v>329.1303360432387</v>
       </c>
       <c r="X26" t="n">
-        <v>414.4985050212281</v>
+        <v>329.1303360432387</v>
       </c>
       <c r="Y26" t="n">
-        <v>414.4985050212281</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="27">
@@ -6272,40 +6272,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>528.4364174409648</v>
+        <v>459.9709454081444</v>
       </c>
       <c r="C27" t="n">
-        <v>528.4364174409648</v>
+        <v>314.4154782914583</v>
       </c>
       <c r="D27" t="n">
-        <v>396.1761276453055</v>
+        <v>182.155188495799</v>
       </c>
       <c r="E27" t="n">
-        <v>269.2346152999393</v>
+        <v>55.21367615043273</v>
       </c>
       <c r="F27" t="n">
-        <v>145.3596230394576</v>
+        <v>31.84</v>
       </c>
       <c r="G27" t="n">
-        <v>145.3596230394576</v>
+        <v>31.84</v>
       </c>
       <c r="H27" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I27" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J27" t="n">
-        <v>182.7552848922805</v>
+        <v>182.7552848922801</v>
       </c>
       <c r="K27" t="n">
-        <v>418.0249238168525</v>
+        <v>418.0249238168522</v>
       </c>
       <c r="L27" t="n">
-        <v>751.3313599403546</v>
+        <v>751.3313599403541</v>
       </c>
       <c r="M27" t="n">
-        <v>909.7116016832138</v>
+        <v>909.7116016832133</v>
       </c>
       <c r="N27" t="n">
         <v>1117.20514421531</v>
@@ -6314,34 +6314,34 @@
         <v>1424.13822816318</v>
       </c>
       <c r="P27" t="n">
-        <v>1591.155790368536</v>
+        <v>1591.155790368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R27" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="S27" t="n">
-        <v>1471.378592739353</v>
+        <v>1592</v>
       </c>
       <c r="T27" t="n">
-        <v>1471.378592739353</v>
+        <v>1402.913120706533</v>
       </c>
       <c r="U27" t="n">
-        <v>1286.336777086792</v>
+        <v>1217.871305053971</v>
       </c>
       <c r="V27" t="n">
-        <v>1086.831052650913</v>
+        <v>1018.365580618092</v>
       </c>
       <c r="W27" t="n">
-        <v>1086.831052650913</v>
+        <v>1018.365580618092</v>
       </c>
       <c r="X27" t="n">
-        <v>881.9191946252688</v>
+        <v>813.4537225924485</v>
       </c>
       <c r="Y27" t="n">
-        <v>697.6854645584664</v>
+        <v>629.219992525646</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>143.9194637516636</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="C28" t="n">
-        <v>87.63133582434575</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="D28" t="n">
-        <v>87.63133582434575</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="E28" t="n">
-        <v>41.55993197878387</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="F28" t="n">
-        <v>41.55993197878387</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="G28" t="n">
-        <v>41.55993197878387</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="H28" t="n">
-        <v>31.84000000000037</v>
+        <v>103.6260309695083</v>
       </c>
       <c r="I28" t="n">
-        <v>78.99696549346032</v>
+        <v>150.7829964629683</v>
       </c>
       <c r="J28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="K28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="L28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="M28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="N28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="O28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="P28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="Q28" t="n">
-        <v>275.8237687688625</v>
+        <v>347.6097997383704</v>
       </c>
       <c r="R28" t="n">
-        <v>275.8237687688625</v>
+        <v>31.84</v>
       </c>
       <c r="S28" t="n">
-        <v>133.2355213458755</v>
+        <v>31.84</v>
       </c>
       <c r="T28" t="n">
-        <v>141.1633349309099</v>
+        <v>39.76781358503438</v>
       </c>
       <c r="U28" t="n">
-        <v>206.5575760937867</v>
+        <v>105.1620547479112</v>
       </c>
       <c r="V28" t="n">
-        <v>224.2089689797326</v>
+        <v>122.8134476338572</v>
       </c>
       <c r="W28" t="n">
-        <v>214.7414842941673</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="X28" t="n">
-        <v>214.7414842941673</v>
+        <v>113.3459629482918</v>
       </c>
       <c r="Y28" t="n">
-        <v>214.7414842941673</v>
+        <v>113.3459629482918</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>688.4913518039357</v>
+        <v>687.335179291623</v>
       </c>
       <c r="C29" t="n">
-        <v>688.4913518039357</v>
+        <v>687.335179291623</v>
       </c>
       <c r="D29" t="n">
-        <v>519.4619015616631</v>
+        <v>518.3057290493505</v>
       </c>
       <c r="E29" t="n">
-        <v>356.4686797365433</v>
+        <v>518.3057290493505</v>
       </c>
       <c r="F29" t="n">
-        <v>192.943802253703</v>
+        <v>354.7808515665103</v>
       </c>
       <c r="G29" t="n">
-        <v>192.943802253703</v>
+        <v>192.9438022537026</v>
       </c>
       <c r="H29" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I29" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J29" t="n">
-        <v>425.8600000000055</v>
+        <v>425.8600000000096</v>
       </c>
       <c r="K29" t="n">
-        <v>490.8302757958045</v>
+        <v>675.7435649003232</v>
       </c>
       <c r="L29" t="n">
-        <v>574.9900464490709</v>
+        <v>759.9033355535895</v>
       </c>
       <c r="M29" t="n">
-        <v>969.0100464490761</v>
+        <v>1101.26328323319</v>
       </c>
       <c r="N29" t="n">
-        <v>1101.263283233212</v>
+        <v>1495.283283233199</v>
       </c>
       <c r="O29" t="n">
-        <v>1121.574043410137</v>
+        <v>1515.594043410124</v>
       </c>
       <c r="P29" t="n">
-        <v>1197.980000000013</v>
+        <v>1592</v>
       </c>
       <c r="Q29" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R29" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="S29" t="n">
-        <v>1592.000000000019</v>
+        <v>1350.0073834188</v>
       </c>
       <c r="T29" t="n">
-        <v>1592.000000000019</v>
+        <v>1078.093789561142</v>
       </c>
       <c r="U29" t="n">
-        <v>1189.979797979806</v>
+        <v>1078.093789561142</v>
       </c>
       <c r="V29" t="n">
-        <v>929.9047992338089</v>
+        <v>687.335179291623</v>
       </c>
       <c r="W29" t="n">
-        <v>929.9047992338089</v>
+        <v>687.335179291623</v>
       </c>
       <c r="X29" t="n">
-        <v>929.9047992338089</v>
+        <v>687.335179291623</v>
       </c>
       <c r="Y29" t="n">
-        <v>929.9047992338089</v>
+        <v>687.335179291623</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>538.7059074373179</v>
+        <v>525.2840181314085</v>
       </c>
       <c r="C30" t="n">
-        <v>419.4130665832581</v>
+        <v>405.9911772773486</v>
       </c>
       <c r="D30" t="n">
-        <v>313.4154030502251</v>
+        <v>299.9935137443156</v>
       </c>
       <c r="E30" t="n">
-        <v>212.7365169674851</v>
+        <v>299.9935137443156</v>
       </c>
       <c r="F30" t="n">
-        <v>115.1241509696297</v>
+        <v>202.3811477464602</v>
       </c>
       <c r="G30" t="n">
-        <v>31.84000000000037</v>
+        <v>119.0969967768309</v>
       </c>
       <c r="H30" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I30" t="n">
-        <v>32.6842096314831</v>
+        <v>31.84</v>
       </c>
       <c r="J30" t="n">
-        <v>183.5994945237632</v>
+        <v>182.7552848922801</v>
       </c>
       <c r="K30" t="n">
-        <v>418.8691334483353</v>
+        <v>418.0249238168522</v>
       </c>
       <c r="L30" t="n">
-        <v>752.1755695718373</v>
+        <v>751.3313599403541</v>
       </c>
       <c r="M30" t="n">
-        <v>910.5558113146965</v>
+        <v>909.7116016832133</v>
       </c>
       <c r="N30" t="n">
-        <v>1118.049353846793</v>
+        <v>1117.20514421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1424.982437794663</v>
+        <v>1424.13822816318</v>
       </c>
       <c r="P30" t="n">
-        <v>1592.000000000019</v>
+        <v>1591.155790368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R30" t="n">
-        <v>1592.000000000019</v>
+        <v>1499.737315147507</v>
       </c>
       <c r="S30" t="n">
-        <v>1592.000000000019</v>
+        <v>1499.737315147507</v>
       </c>
       <c r="T30" t="n">
-        <v>1429.175746969177</v>
+        <v>1336.913062116666</v>
       </c>
       <c r="U30" t="n">
-        <v>1270.396557579242</v>
+        <v>1178.13387272673</v>
       </c>
       <c r="V30" t="n">
-        <v>1097.153459405989</v>
+        <v>1004.890774553478</v>
       </c>
       <c r="W30" t="n">
-        <v>1018.312663859387</v>
+        <v>1004.890774553478</v>
       </c>
       <c r="X30" t="n">
-        <v>839.6634320963694</v>
+        <v>826.24154279046</v>
       </c>
       <c r="Y30" t="n">
-        <v>681.6923282921933</v>
+        <v>668.2704389862839</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="C31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="D31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="E31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="F31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="G31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="H31" t="n">
-        <v>232.7078605611292</v>
+        <v>232.7078605611289</v>
       </c>
       <c r="I31" t="n">
-        <v>305.6048260545892</v>
+        <v>305.6048260545888</v>
       </c>
       <c r="J31" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="K31" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="L31" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="M31" t="n">
-        <v>325.9891570056765</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="N31" t="n">
-        <v>31.84000000000037</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="O31" t="n">
-        <v>31.84000000000037</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="P31" t="n">
-        <v>31.84000000000037</v>
+        <v>433.8602020202118</v>
       </c>
       <c r="Q31" t="n">
-        <v>31.84000000000037</v>
+        <v>433.8602020202118</v>
       </c>
       <c r="R31" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="T31" t="n">
-        <v>65.50781358503474</v>
+        <v>65.50781358503436</v>
       </c>
       <c r="U31" t="n">
-        <v>156.6420547479115</v>
+        <v>156.6420547479112</v>
       </c>
       <c r="V31" t="n">
-        <v>200.0334476338575</v>
+        <v>200.0334476338572</v>
       </c>
       <c r="W31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="X31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="Y31" t="n">
-        <v>216.4943658935349</v>
+        <v>216.4943658935346</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>409.4296302857011</v>
+        <v>559.881625693778</v>
       </c>
       <c r="C32" t="n">
-        <v>200.8694502422729</v>
+        <v>559.881625693778</v>
       </c>
       <c r="D32" t="n">
-        <v>31.84000000000037</v>
+        <v>559.881625693778</v>
       </c>
       <c r="E32" t="n">
-        <v>31.84000000000037</v>
+        <v>396.8884038686581</v>
       </c>
       <c r="F32" t="n">
-        <v>31.84000000000037</v>
+        <v>233.3635263858179</v>
       </c>
       <c r="G32" t="n">
-        <v>31.84000000000037</v>
+        <v>71.52647707301026</v>
       </c>
       <c r="H32" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I32" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J32" t="n">
-        <v>42.41114914399412</v>
+        <v>425.8600000000096</v>
       </c>
       <c r="K32" t="n">
-        <v>110.2497399982655</v>
+        <v>675.743564900338</v>
       </c>
       <c r="L32" t="n">
-        <v>313.223283233202</v>
+        <v>759.9033355536044</v>
       </c>
       <c r="M32" t="n">
-        <v>707.2432832332072</v>
+        <v>759.9033355536044</v>
       </c>
       <c r="N32" t="n">
-        <v>1101.263283233212</v>
+        <v>759.9033355536044</v>
       </c>
       <c r="O32" t="n">
-        <v>1121.574043410137</v>
+        <v>1153.923335553614</v>
       </c>
       <c r="P32" t="n">
-        <v>1197.980000000013</v>
+        <v>1547.943335553623</v>
       </c>
       <c r="Q32" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R32" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="S32" t="n">
-        <v>1592.000000000019</v>
+        <v>1350.0073834188</v>
       </c>
       <c r="T32" t="n">
-        <v>1592.000000000019</v>
+        <v>1350.0073834188</v>
       </c>
       <c r="U32" t="n">
-        <v>1592.000000000019</v>
+        <v>1350.0073834188</v>
       </c>
       <c r="V32" t="n">
-        <v>1432.634420310369</v>
+        <v>959.2487731492806</v>
       </c>
       <c r="W32" t="n">
-        <v>1033.267272854867</v>
+        <v>559.881625693778</v>
       </c>
       <c r="X32" t="n">
-        <v>680.4573400663137</v>
+        <v>559.881625693778</v>
       </c>
       <c r="Y32" t="n">
-        <v>409.4296302857011</v>
+        <v>559.881625693778</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>617.5467029839202</v>
+        <v>542.6787532445193</v>
       </c>
       <c r="C33" t="n">
-        <v>498.2538621298603</v>
+        <v>423.3859123904594</v>
       </c>
       <c r="D33" t="n">
-        <v>400.6723998270561</v>
+        <v>317.3882488574264</v>
       </c>
       <c r="E33" t="n">
-        <v>299.993513744316</v>
+        <v>216.7093627746864</v>
       </c>
       <c r="F33" t="n">
-        <v>202.3811477464606</v>
+        <v>119.096996776831</v>
       </c>
       <c r="G33" t="n">
-        <v>119.0969967768313</v>
+        <v>119.096996776831</v>
       </c>
       <c r="H33" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I33" t="n">
-        <v>31.84000000000037</v>
+        <v>32.68420963146446</v>
       </c>
       <c r="J33" t="n">
-        <v>182.7552848922805</v>
+        <v>183.5994945237445</v>
       </c>
       <c r="K33" t="n">
-        <v>418.0249238168525</v>
+        <v>418.8691334483166</v>
       </c>
       <c r="L33" t="n">
-        <v>751.3313599403546</v>
+        <v>752.1755695718186</v>
       </c>
       <c r="M33" t="n">
-        <v>909.7116016832138</v>
+        <v>910.5558113146778</v>
       </c>
       <c r="N33" t="n">
-        <v>1117.20514421531</v>
+        <v>1118.049353846774</v>
       </c>
       <c r="O33" t="n">
-        <v>1424.13822816318</v>
+        <v>1424.982437794644</v>
       </c>
       <c r="P33" t="n">
-        <v>1591.155790368536</v>
+        <v>1592</v>
       </c>
       <c r="Q33" t="n">
-        <v>1592.000000000018</v>
+        <v>1592</v>
       </c>
       <c r="R33" t="n">
-        <v>1592.000000000018</v>
+        <v>1592</v>
       </c>
       <c r="S33" t="n">
-        <v>1592.000000000018</v>
+        <v>1592</v>
       </c>
       <c r="T33" t="n">
-        <v>1429.175746969177</v>
+        <v>1429.175746969159</v>
       </c>
       <c r="U33" t="n">
-        <v>1270.396557579242</v>
+        <v>1270.396557579224</v>
       </c>
       <c r="V33" t="n">
-        <v>1097.153459405989</v>
+        <v>1097.153459405971</v>
       </c>
       <c r="W33" t="n">
-        <v>1097.153459405989</v>
+        <v>1022.285509666588</v>
       </c>
       <c r="X33" t="n">
-        <v>918.5042276429717</v>
+        <v>843.6362779035708</v>
       </c>
       <c r="Y33" t="n">
-        <v>760.5331238387956</v>
+        <v>685.6651740993947</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>171.5798680657952</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="C34" t="n">
-        <v>171.5798680657952</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="D34" t="n">
-        <v>171.5798680657952</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="E34" t="n">
-        <v>171.5798680657952</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="F34" t="n">
-        <v>139.8800135529246</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="G34" t="n">
-        <v>139.8800135529246</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="H34" t="n">
-        <v>156.0935082205189</v>
+        <v>232.7078605611289</v>
       </c>
       <c r="I34" t="n">
-        <v>228.9904737139788</v>
+        <v>305.6048260545888</v>
       </c>
       <c r="J34" t="n">
-        <v>451.557276989381</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="K34" t="n">
-        <v>451.557276989381</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="L34" t="n">
-        <v>451.557276989381</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="M34" t="n">
-        <v>451.557276989381</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="N34" t="n">
-        <v>451.557276989381</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="O34" t="n">
-        <v>451.557276989381</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="P34" t="n">
-        <v>433.8602020202077</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="Q34" t="n">
-        <v>31.84000000000037</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="R34" t="n">
-        <v>31.84000000000037</v>
+        <v>126.1514273097791</v>
       </c>
       <c r="S34" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="T34" t="n">
-        <v>65.50781358503474</v>
+        <v>65.50781358503437</v>
       </c>
       <c r="U34" t="n">
-        <v>156.6420547479116</v>
+        <v>156.6420547479112</v>
       </c>
       <c r="V34" t="n">
-        <v>200.0334476338575</v>
+        <v>200.0334476338572</v>
       </c>
       <c r="W34" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="X34" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="Y34" t="n">
-        <v>171.5798680657952</v>
+        <v>216.4943658935346</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>409.4296302857011</v>
+        <v>178.0365997058125</v>
       </c>
       <c r="C35" t="n">
-        <v>200.8694502422729</v>
+        <v>178.0365997058125</v>
       </c>
       <c r="D35" t="n">
-        <v>31.84000000000037</v>
+        <v>178.0365997058125</v>
       </c>
       <c r="E35" t="n">
-        <v>31.84000000000037</v>
+        <v>178.0365997058125</v>
       </c>
       <c r="F35" t="n">
-        <v>31.84000000000037</v>
+        <v>178.0365997058125</v>
       </c>
       <c r="G35" t="n">
-        <v>31.84000000000037</v>
+        <v>178.0365997058125</v>
       </c>
       <c r="H35" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I35" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J35" t="n">
-        <v>425.8600000000055</v>
+        <v>42.41114914399374</v>
       </c>
       <c r="K35" t="n">
-        <v>493.6985908542769</v>
+        <v>110.2497399982651</v>
       </c>
       <c r="L35" t="n">
-        <v>574.9900464490702</v>
+        <v>313.2232832331642</v>
       </c>
       <c r="M35" t="n">
-        <v>707.2432832332072</v>
+        <v>707.2432832331758</v>
       </c>
       <c r="N35" t="n">
-        <v>1101.263283233212</v>
+        <v>1101.263283233187</v>
       </c>
       <c r="O35" t="n">
-        <v>1121.574043410137</v>
+        <v>1121.574043410112</v>
       </c>
       <c r="P35" t="n">
-        <v>1197.980000000013</v>
+        <v>1197.979999999988</v>
       </c>
       <c r="Q35" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R35" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="S35" t="n">
-        <v>1350.007383418818</v>
+        <v>1592</v>
       </c>
       <c r="T35" t="n">
-        <v>1350.007383418818</v>
+        <v>1592</v>
       </c>
       <c r="U35" t="n">
-        <v>947.987181398606</v>
+        <v>1592</v>
       </c>
       <c r="V35" t="n">
-        <v>947.987181398606</v>
+        <v>1201.241389730481</v>
       </c>
       <c r="W35" t="n">
-        <v>947.987181398606</v>
+        <v>801.8742422749783</v>
       </c>
       <c r="X35" t="n">
-        <v>921.8707874961869</v>
+        <v>449.064309486425</v>
       </c>
       <c r="Y35" t="n">
-        <v>650.8430777155744</v>
+        <v>178.0365997058125</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>625.9629042141489</v>
+        <v>625.9629042141485</v>
       </c>
       <c r="C36" t="n">
-        <v>506.670063360089</v>
+        <v>506.6700633600886</v>
       </c>
       <c r="D36" t="n">
-        <v>400.6723998270561</v>
+        <v>400.6723998270556</v>
       </c>
       <c r="E36" t="n">
-        <v>299.993513744316</v>
+        <v>299.9935137443156</v>
       </c>
       <c r="F36" t="n">
-        <v>202.3811477464606</v>
+        <v>202.3811477464602</v>
       </c>
       <c r="G36" t="n">
-        <v>119.0969967768313</v>
+        <v>119.0969967768309</v>
       </c>
       <c r="H36" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I36" t="n">
-        <v>32.68420963148287</v>
+        <v>31.84</v>
       </c>
       <c r="J36" t="n">
-        <v>183.599494523763</v>
+        <v>182.7552848922801</v>
       </c>
       <c r="K36" t="n">
-        <v>418.869133448335</v>
+        <v>418.0249238168522</v>
       </c>
       <c r="L36" t="n">
-        <v>752.1755695718371</v>
+        <v>751.3313599403541</v>
       </c>
       <c r="M36" t="n">
-        <v>910.5558113146963</v>
+        <v>909.7116016832133</v>
       </c>
       <c r="N36" t="n">
-        <v>1118.049353846793</v>
+        <v>1117.20514421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1424.982437794663</v>
+        <v>1424.13822816318</v>
       </c>
       <c r="P36" t="n">
-        <v>1592.000000000018</v>
+        <v>1591.155790368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>1592.000000000018</v>
+        <v>1592</v>
       </c>
       <c r="R36" t="n">
-        <v>1592.000000000018</v>
+        <v>1592</v>
       </c>
       <c r="S36" t="n">
-        <v>1592.000000000018</v>
+        <v>1592</v>
       </c>
       <c r="T36" t="n">
-        <v>1429.175746969177</v>
+        <v>1429.175746969159</v>
       </c>
       <c r="U36" t="n">
-        <v>1270.396557579242</v>
+        <v>1270.396557579224</v>
       </c>
       <c r="V36" t="n">
-        <v>1097.153459405989</v>
+        <v>1097.153459405971</v>
       </c>
       <c r="W36" t="n">
-        <v>947.598556832042</v>
+        <v>1097.153459405971</v>
       </c>
       <c r="X36" t="n">
-        <v>768.9493250690243</v>
+        <v>918.5042276429531</v>
       </c>
       <c r="Y36" t="n">
-        <v>768.9493250690243</v>
+        <v>768.9493250690239</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="C37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="D37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="E37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="F37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="G37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="H37" t="n">
-        <v>232.7078605611293</v>
+        <v>232.7078605611289</v>
       </c>
       <c r="I37" t="n">
-        <v>305.6048260545892</v>
+        <v>305.6048260545888</v>
       </c>
       <c r="J37" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="K37" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="L37" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="M37" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="N37" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="O37" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="P37" t="n">
-        <v>528.1716293299913</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="Q37" t="n">
-        <v>433.8602020202077</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="R37" t="n">
-        <v>31.84000000000037</v>
+        <v>148.1656211603607</v>
       </c>
       <c r="S37" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="T37" t="n">
-        <v>65.50781358503474</v>
+        <v>65.50781358503436</v>
       </c>
       <c r="U37" t="n">
-        <v>156.6420547479116</v>
+        <v>156.6420547479112</v>
       </c>
       <c r="V37" t="n">
-        <v>200.0334476338575</v>
+        <v>200.0334476338572</v>
       </c>
       <c r="W37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="X37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="Y37" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.84000000000037</v>
+        <v>717.8353257194074</v>
       </c>
       <c r="C38" t="n">
-        <v>31.84000000000037</v>
+        <v>509.2751456759792</v>
       </c>
       <c r="D38" t="n">
-        <v>31.84000000000037</v>
+        <v>340.2456954337066</v>
       </c>
       <c r="E38" t="n">
-        <v>31.84000000000037</v>
+        <v>177.2524736085867</v>
       </c>
       <c r="F38" t="n">
-        <v>31.84000000000037</v>
+        <v>177.2524736085867</v>
       </c>
       <c r="G38" t="n">
-        <v>31.84000000000037</v>
+        <v>177.2524736085867</v>
       </c>
       <c r="H38" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I38" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J38" t="n">
-        <v>42.41114914399412</v>
+        <v>42.41114914399374</v>
       </c>
       <c r="K38" t="n">
-        <v>110.2497399982655</v>
+        <v>229.0635125799033</v>
       </c>
       <c r="L38" t="n">
-        <v>313.223283233202</v>
+        <v>313.2232832331696</v>
       </c>
       <c r="M38" t="n">
-        <v>707.2432832332072</v>
+        <v>707.2432832331795</v>
       </c>
       <c r="N38" t="n">
-        <v>1101.263283233212</v>
+        <v>1101.263283233189</v>
       </c>
       <c r="O38" t="n">
-        <v>1121.574043410137</v>
+        <v>1121.574043410114</v>
       </c>
       <c r="P38" t="n">
-        <v>1197.980000000013</v>
+        <v>1197.97999999999</v>
       </c>
       <c r="Q38" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R38" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="S38" t="n">
-        <v>1350.007383418818</v>
+        <v>1350.0073834188</v>
       </c>
       <c r="T38" t="n">
-        <v>1005.242281322558</v>
+        <v>1350.0073834188</v>
       </c>
       <c r="U38" t="n">
-        <v>603.2220793023436</v>
+        <v>1350.0073834188</v>
       </c>
       <c r="V38" t="n">
-        <v>431.207147455503</v>
+        <v>959.2487731492806</v>
       </c>
       <c r="W38" t="n">
-        <v>31.84000000000037</v>
+        <v>959.2487731492806</v>
       </c>
       <c r="X38" t="n">
-        <v>31.84000000000037</v>
+        <v>959.2487731492806</v>
       </c>
       <c r="Y38" t="n">
-        <v>31.84000000000037</v>
+        <v>959.2487731492806</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>151.1328408540603</v>
+        <v>617.5467029839016</v>
       </c>
       <c r="C39" t="n">
-        <v>31.84000000000037</v>
+        <v>498.2538621298417</v>
       </c>
       <c r="D39" t="n">
-        <v>31.84000000000037</v>
+        <v>392.2561985968087</v>
       </c>
       <c r="E39" t="n">
-        <v>31.84000000000037</v>
+        <v>291.5773125140687</v>
       </c>
       <c r="F39" t="n">
-        <v>31.84000000000037</v>
+        <v>193.9649465162133</v>
       </c>
       <c r="G39" t="n">
-        <v>31.84000000000037</v>
+        <v>110.680795546584</v>
       </c>
       <c r="H39" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I39" t="n">
-        <v>32.6842096314831</v>
+        <v>32.68420963146446</v>
       </c>
       <c r="J39" t="n">
-        <v>183.5994945237632</v>
+        <v>183.5994945237445</v>
       </c>
       <c r="K39" t="n">
-        <v>418.8691334483353</v>
+        <v>418.8691334483166</v>
       </c>
       <c r="L39" t="n">
-        <v>752.1755695718373</v>
+        <v>752.1755695718186</v>
       </c>
       <c r="M39" t="n">
-        <v>910.5558113146965</v>
+        <v>910.5558113146778</v>
       </c>
       <c r="N39" t="n">
-        <v>1118.049353846793</v>
+        <v>1118.049353846774</v>
       </c>
       <c r="O39" t="n">
-        <v>1424.982437794663</v>
+        <v>1424.982437794644</v>
       </c>
       <c r="P39" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="Q39" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R39" t="n">
-        <v>1537.286606182438</v>
+        <v>1592</v>
       </c>
       <c r="S39" t="n">
-        <v>1316.872140809379</v>
+        <v>1592</v>
       </c>
       <c r="T39" t="n">
-        <v>1154.047887778538</v>
+        <v>1429.175746969159</v>
       </c>
       <c r="U39" t="n">
-        <v>995.2686983886031</v>
+        <v>1270.396557579224</v>
       </c>
       <c r="V39" t="n">
-        <v>822.0256002153503</v>
+        <v>1097.153459405971</v>
       </c>
       <c r="W39" t="n">
-        <v>630.7395972761295</v>
+        <v>1097.153459405971</v>
       </c>
       <c r="X39" t="n">
-        <v>452.0903655131118</v>
+        <v>918.5042276429531</v>
       </c>
       <c r="Y39" t="n">
-        <v>294.1192617089357</v>
+        <v>760.533123838777</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>171.9349716136575</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="C40" t="n">
-        <v>171.9349716136575</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="D40" t="n">
-        <v>128.9690947898641</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="E40" t="n">
-        <v>128.9690947898641</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="F40" t="n">
-        <v>128.9690947898641</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="G40" t="n">
-        <v>128.9690947898641</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="H40" t="n">
-        <v>145.1825894574584</v>
+        <v>232.7078605611289</v>
       </c>
       <c r="I40" t="n">
-        <v>218.0795549509184</v>
+        <v>305.6048260545888</v>
       </c>
       <c r="J40" t="n">
-        <v>440.6463582263204</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="K40" t="n">
-        <v>440.6463582263204</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="L40" t="n">
-        <v>440.6463582263204</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="M40" t="n">
-        <v>440.6463582263204</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="N40" t="n">
-        <v>440.6463582263204</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="O40" t="n">
-        <v>440.6463582263204</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="P40" t="n">
-        <v>440.6463582263204</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="Q40" t="n">
-        <v>148.1656211603611</v>
+        <v>528.1716293299909</v>
       </c>
       <c r="R40" t="n">
-        <v>148.1656211603611</v>
+        <v>148.1656211603607</v>
       </c>
       <c r="S40" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="T40" t="n">
-        <v>65.50781358503474</v>
+        <v>65.50781358503437</v>
       </c>
       <c r="U40" t="n">
-        <v>156.6420547479116</v>
+        <v>156.6420547479112</v>
       </c>
       <c r="V40" t="n">
-        <v>200.0334476338575</v>
+        <v>200.0334476338572</v>
       </c>
       <c r="W40" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="X40" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
       <c r="Y40" t="n">
-        <v>216.494365893535</v>
+        <v>216.4943658935346</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="C41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="D41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="E41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="F41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="G41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="H41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="I41" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J41" t="n">
-        <v>42.41114914399412</v>
+        <v>425.8600000000098</v>
       </c>
       <c r="K41" t="n">
-        <v>436.4311491439987</v>
+        <v>493.6985908542811</v>
       </c>
       <c r="L41" t="n">
-        <v>520.5909197972651</v>
+        <v>577.8583615075474</v>
       </c>
       <c r="M41" t="n">
-        <v>914.6109197972703</v>
+        <v>707.2432832331795</v>
       </c>
       <c r="N41" t="n">
-        <v>1308.630919797276</v>
+        <v>1101.263283233189</v>
       </c>
       <c r="O41" t="n">
-        <v>1328.9416799742</v>
+        <v>1121.574043410114</v>
       </c>
       <c r="P41" t="n">
-        <v>1405.347636564076</v>
+        <v>1197.97999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R41" t="n">
-        <v>1494.990004736679</v>
+        <v>1592</v>
       </c>
       <c r="S41" t="n">
-        <v>1494.990004736679</v>
+        <v>1592</v>
       </c>
       <c r="T41" t="n">
-        <v>1494.990004736679</v>
+        <v>1592</v>
       </c>
       <c r="U41" t="n">
-        <v>1092.969802716466</v>
+        <v>1189.979797979759</v>
       </c>
       <c r="V41" t="n">
-        <v>690.9496006962538</v>
+        <v>844.2775553366253</v>
       </c>
       <c r="W41" t="n">
-        <v>288.9293986760424</v>
+        <v>442.2573533163869</v>
       </c>
       <c r="X41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
       <c r="Y41" t="n">
-        <v>40.23715129614897</v>
+        <v>40.2371512961486</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>118.9135363491803</v>
+        <v>756.7640197904653</v>
       </c>
       <c r="C42" t="n">
-        <v>118.9135363491803</v>
+        <v>756.7640197904653</v>
       </c>
       <c r="D42" t="n">
-        <v>118.9135363491803</v>
+        <v>756.7640197904653</v>
       </c>
       <c r="E42" t="n">
-        <v>118.9135363491803</v>
+        <v>756.7640197904653</v>
       </c>
       <c r="F42" t="n">
-        <v>118.9135363491803</v>
+        <v>535.9193305602867</v>
       </c>
       <c r="G42" t="n">
-        <v>118.9135363491803</v>
+        <v>329.4028563583341</v>
       </c>
       <c r="H42" t="n">
-        <v>118.9135363491803</v>
+        <v>118.9135363491799</v>
       </c>
       <c r="I42" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J42" t="n">
-        <v>182.7552848922805</v>
+        <v>182.7552848922801</v>
       </c>
       <c r="K42" t="n">
-        <v>418.8691334483353</v>
+        <v>418.0249238168522</v>
       </c>
       <c r="L42" t="n">
-        <v>752.1755695718373</v>
+        <v>751.3313599403541</v>
       </c>
       <c r="M42" t="n">
-        <v>910.5558113146965</v>
+        <v>909.7116016832133</v>
       </c>
       <c r="N42" t="n">
-        <v>1118.049353846793</v>
+        <v>1118.049353846774</v>
       </c>
       <c r="O42" t="n">
-        <v>1424.982437794663</v>
+        <v>1424.982437794644</v>
       </c>
       <c r="P42" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="Q42" t="n">
-        <v>1576.558165622366</v>
+        <v>1576.558165622348</v>
       </c>
       <c r="R42" t="n">
-        <v>1174.537963602149</v>
+        <v>1576.558165622348</v>
       </c>
       <c r="S42" t="n">
-        <v>830.8911749967672</v>
+        <v>1309.039340140828</v>
       </c>
       <c r="T42" t="n">
-        <v>544.8345987336029</v>
+        <v>1022.982763877664</v>
       </c>
       <c r="U42" t="n">
-        <v>262.8230861113445</v>
+        <v>1022.982763877664</v>
       </c>
       <c r="V42" t="n">
-        <v>118.9135363491803</v>
+        <v>1022.982763877664</v>
       </c>
       <c r="W42" t="n">
-        <v>118.9135363491803</v>
+        <v>1022.982763877664</v>
       </c>
       <c r="X42" t="n">
-        <v>118.9135363491803</v>
+        <v>1022.982763877664</v>
       </c>
       <c r="Y42" t="n">
-        <v>118.9135363491803</v>
+        <v>1022.982763877664</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="C43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="D43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="E43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="F43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="G43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="H43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="K43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="L43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="M43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="N43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="P43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="Q43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="R43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="S43" t="n">
-        <v>133.6268032754025</v>
+        <v>133.6268032754021</v>
       </c>
       <c r="T43" t="n">
-        <v>133.6268032754025</v>
+        <v>110.7999093093093</v>
       </c>
       <c r="U43" t="n">
-        <v>133.6268032754025</v>
+        <v>110.7999093093093</v>
       </c>
       <c r="V43" t="n">
-        <v>133.6268032754025</v>
+        <v>31.84</v>
       </c>
       <c r="W43" t="n">
-        <v>133.6268032754025</v>
+        <v>31.84</v>
       </c>
       <c r="X43" t="n">
-        <v>133.6268032754025</v>
+        <v>31.84</v>
       </c>
       <c r="Y43" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>787.9595959595963</v>
+        <v>387.9327864675421</v>
       </c>
       <c r="C44" t="n">
-        <v>787.9595959595963</v>
+        <v>387.9327864675421</v>
       </c>
       <c r="D44" t="n">
-        <v>701.7079127487088</v>
+        <v>387.9327864675421</v>
       </c>
       <c r="E44" t="n">
-        <v>385.1793373882355</v>
+        <v>387.9327864675421</v>
       </c>
       <c r="F44" t="n">
-        <v>385.1793373882355</v>
+        <v>387.9327864675421</v>
       </c>
       <c r="G44" t="n">
-        <v>385.1793373882355</v>
+        <v>71.55028260927992</v>
       </c>
       <c r="H44" t="n">
-        <v>70.54018159917928</v>
+        <v>71.55028260927992</v>
       </c>
       <c r="I44" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J44" t="n">
-        <v>425.8600000000046</v>
+        <v>42.41114914399374</v>
       </c>
       <c r="K44" t="n">
-        <v>493.6985908542759</v>
+        <v>436.4311491439937</v>
       </c>
       <c r="L44" t="n">
-        <v>577.8583615075423</v>
+        <v>520.59091979726</v>
       </c>
       <c r="M44" t="n">
-        <v>707.243283233209</v>
+        <v>914.6109197972701</v>
       </c>
       <c r="N44" t="n">
-        <v>1101.263283233213</v>
+        <v>1308.63091979728</v>
       </c>
       <c r="O44" t="n">
-        <v>1121.574043410138</v>
+        <v>1328.941679974205</v>
       </c>
       <c r="P44" t="n">
-        <v>1197.980000000014</v>
+        <v>1405.347636564081</v>
       </c>
       <c r="Q44" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="R44" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="S44" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="T44" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="U44" t="n">
-        <v>1189.979797979805</v>
+        <v>1191.973190507946</v>
       </c>
       <c r="V44" t="n">
-        <v>1189.979797979805</v>
+        <v>789.9529884877441</v>
       </c>
       <c r="W44" t="n">
-        <v>1189.979797979805</v>
+        <v>789.9529884877441</v>
       </c>
       <c r="X44" t="n">
-        <v>787.9595959595963</v>
+        <v>387.9327864675421</v>
       </c>
       <c r="Y44" t="n">
-        <v>787.9595959595963</v>
+        <v>387.9327864675421</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>268.6595045049833</v>
+        <v>1212.050348000744</v>
       </c>
       <c r="C45" t="n">
-        <v>268.6595045049833</v>
+        <v>1212.050348000744</v>
       </c>
       <c r="D45" t="n">
-        <v>268.6595045049833</v>
+        <v>951.5072299222567</v>
       </c>
       <c r="E45" t="n">
-        <v>268.6595045049833</v>
+        <v>882.0165450429906</v>
       </c>
       <c r="F45" t="n">
-        <v>268.6595045049833</v>
+        <v>629.8587244996806</v>
       </c>
       <c r="G45" t="n">
-        <v>31.84000000000037</v>
+        <v>392.0291189845967</v>
       </c>
       <c r="H45" t="n">
-        <v>31.84000000000037</v>
+        <v>150.2266676623113</v>
       </c>
       <c r="I45" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J45" t="n">
-        <v>182.7552848922805</v>
+        <v>182.7552848922801</v>
       </c>
       <c r="K45" t="n">
-        <v>418.0249238168525</v>
+        <v>418.8691334483166</v>
       </c>
       <c r="L45" t="n">
-        <v>751.3313599403546</v>
+        <v>752.1755695718186</v>
       </c>
       <c r="M45" t="n">
-        <v>910.5558113146965</v>
+        <v>910.5558113146778</v>
       </c>
       <c r="N45" t="n">
-        <v>1118.049353846793</v>
+        <v>1118.049353846774</v>
       </c>
       <c r="O45" t="n">
-        <v>1424.982437794663</v>
+        <v>1424.982437794644</v>
       </c>
       <c r="P45" t="n">
-        <v>1592.000000000019</v>
+        <v>1592</v>
       </c>
       <c r="Q45" t="n">
-        <v>1546.255135319336</v>
+        <v>1545.245034309216</v>
       </c>
       <c r="R45" t="n">
-        <v>1546.255135319336</v>
+        <v>1545.245034309216</v>
       </c>
       <c r="S45" t="n">
-        <v>1546.255135319336</v>
+        <v>1545.245034309216</v>
       </c>
       <c r="T45" t="n">
-        <v>1229.895528753141</v>
+        <v>1545.245034309216</v>
       </c>
       <c r="U45" t="n">
-        <v>917.5809858278525</v>
+        <v>1545.245034309216</v>
       </c>
       <c r="V45" t="n">
-        <v>590.8025341192463</v>
+        <v>1545.245034309216</v>
       </c>
       <c r="W45" t="n">
-        <v>268.6595045049833</v>
+        <v>1545.245034309216</v>
       </c>
       <c r="X45" t="n">
-        <v>268.6595045049833</v>
+        <v>1212.050348000744</v>
       </c>
       <c r="Y45" t="n">
-        <v>268.6595045049833</v>
+        <v>1212.050348000744</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="C46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="D46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="E46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="F46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="G46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="H46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="I46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="J46" t="n">
-        <v>103.9268032754025</v>
+        <v>102.9368032754021</v>
       </c>
       <c r="K46" t="n">
-        <v>103.9268032754025</v>
+        <v>102.9368032754021</v>
       </c>
       <c r="L46" t="n">
-        <v>103.9268032754025</v>
+        <v>102.9368032754021</v>
       </c>
       <c r="M46" t="n">
-        <v>103.9268032754025</v>
+        <v>102.9368032754021</v>
       </c>
       <c r="N46" t="n">
-        <v>103.9268032754025</v>
+        <v>31.84</v>
       </c>
       <c r="O46" t="n">
-        <v>103.9268032754025</v>
+        <v>31.84</v>
       </c>
       <c r="P46" t="n">
-        <v>103.9268032754025</v>
+        <v>31.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="R46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="S46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="T46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="U46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="V46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="W46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="X46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
       <c r="Y46" t="n">
-        <v>31.84000000000037</v>
+        <v>31.84</v>
       </c>
     </row>
   </sheetData>
@@ -7967,10 +7967,10 @@
         <v>3.15257157172347</v>
       </c>
       <c r="K2" t="n">
-        <v>626.4761708542713</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>596.83670014897</v>
+        <v>605.4906049324088</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
@@ -7982,7 +7982,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>617.8222660708323</v>
       </c>
       <c r="Q2" t="n">
         <v>128.4803501566311</v>
@@ -8204,10 +8204,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>309.3976294270972</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>609.9901306532663</v>
+        <v>609.9901306532662</v>
       </c>
       <c r="M5" t="n">
         <v>449.6722683458349</v>
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>309.3976294270972</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15257157172347</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>626.4761708542713</v>
       </c>
       <c r="L8" t="n">
-        <v>118.1188818194667</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8456,10 +8456,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>617.8222660708323</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>615.8520732695737</v>
+        <v>298.1648852911679</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>626.4761708542713</v>
+        <v>626.4761708542715</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>56.73674052694264</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>242.2840772103598</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>56.7367405269427</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>626.4761708542713</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>242.2840772103598</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>626.4761708542715</v>
+        <v>626.4761708542713</v>
       </c>
       <c r="L20" t="n">
-        <v>609.9901306532663</v>
+        <v>127.6342270537289</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>381.1285359592824</v>
+        <v>1076.128535959283</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>617.8222660708323</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>139.7764170724176</v>
+        <v>114.6498501566311</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>631.4761708542713</v>
       </c>
       <c r="L23" t="n">
-        <v>618.9901306532664</v>
+        <v>137.4322068517085</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>1085.128535959283</v>
+        <v>1081.128535959283</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>276.4064810477283</v>
+        <v>114.6498501566311</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>387.3220715717293</v>
+        <v>387.3220715717351</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>130.6918401268962</v>
       </c>
       <c r="M26" t="n">
-        <v>847.6722683458406</v>
+        <v>847.6722683458465</v>
       </c>
       <c r="N26" t="n">
-        <v>511.8203760862142</v>
+        <v>779.128535959294</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>512.6498501566369</v>
+        <v>114.6498501566311</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>387.3220715717287</v>
+        <v>387.3220715717331</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>186.7811001055819</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>847.6722683458402</v>
+        <v>794.480296305027</v>
       </c>
       <c r="N29" t="n">
-        <v>514.7176640240666</v>
+        <v>779.1285359592921</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>512.6498501566364</v>
+        <v>114.6498501566311</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>387.3220715717331</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>186.7811001055962</v>
       </c>
       <c r="L32" t="n">
-        <v>122.9111996365082</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>847.6722683458402</v>
+        <v>449.6722683458349</v>
       </c>
       <c r="N32" t="n">
-        <v>779.1285359592877</v>
+        <v>381.1285359592824</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>377.4840806293785</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>320.8222660708418</v>
       </c>
       <c r="Q32" t="n">
-        <v>512.6498501566364</v>
+        <v>159.1515314155974</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>387.3220715717287</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>122.9111996364823</v>
       </c>
       <c r="M35" t="n">
-        <v>583.2613964106197</v>
+        <v>847.6722683458465</v>
       </c>
       <c r="N35" t="n">
-        <v>779.1285359592877</v>
+        <v>779.1285359592941</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>512.6498501566364</v>
+        <v>512.6498501566429</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>122.9111996364864</v>
       </c>
       <c r="L38" t="n">
-        <v>122.9111996365083</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>847.6722683458402</v>
+        <v>847.6722683458447</v>
       </c>
       <c r="N38" t="n">
-        <v>779.1285359592877</v>
+        <v>779.1285359592923</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>512.6498501566364</v>
+        <v>512.649850156641</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>387.3220715717334</v>
       </c>
       <c r="K41" t="n">
-        <v>329.4761708542761</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>847.6722683458402</v>
+        <v>580.3641084727358</v>
       </c>
       <c r="N41" t="n">
-        <v>779.1285359592877</v>
+        <v>779.1285359592923</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>303.1875910010174</v>
+        <v>512.649850156641</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>387.3220715717278</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>329.4761708542713</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>580.3641084727709</v>
+        <v>847.6722683458449</v>
       </c>
       <c r="N44" t="n">
-        <v>779.1285359592868</v>
+        <v>779.1285359592925</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>512.6498501566355</v>
+        <v>303.187591000994</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>111.9372847988301</v>
+        <v>111.9372847988378</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>111.9372847988288</v>
+        <v>111.9372847988224</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23177,22 +23177,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>82.75354582877941</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>134.2076654356193</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.491081552440278</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>229.5841707658304</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>305.605266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>315.7371443745936</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23235,7 +23235,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -23277,10 +23277,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>37.1218509294165</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>436.1782010712237</v>
       </c>
       <c r="V11" t="n">
         <v>416.8510241668239</v>
@@ -23289,10 +23289,10 @@
         <v>425.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>91.15071124901078</v>
       </c>
       <c r="Y11" t="n">
-        <v>298.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23393,7 +23393,7 @@
         <v>67.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>46.12630005553471</v>
+        <v>61.38285596774193</v>
       </c>
       <c r="G13" t="n">
         <v>31.80223349726774</v>
@@ -23414,7 +23414,7 @@
         <v>174.6224478299103</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>269.7535458287794</v>
       </c>
       <c r="N13" t="n">
         <v>321.2076654356193</v>
@@ -23423,7 +23423,7 @@
         <v>393.2909411281953</v>
       </c>
       <c r="P13" t="n">
-        <v>445.2227170004086</v>
+        <v>160.212615259422</v>
       </c>
       <c r="Q13" t="n">
         <v>492.605266425598</v>
@@ -23463,22 +23463,22 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>232.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>193.3391557398498</v>
+        <v>178.2673223309057</v>
       </c>
       <c r="E14" t="n">
-        <v>187.3632896068686</v>
+        <v>186.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>187.8896287080119</v>
+        <v>186.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>186.2186788196795</v>
+        <v>185.2186788196795</v>
       </c>
       <c r="H14" t="n">
-        <v>185.4927642311656</v>
+        <v>184.4927642311656</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>136.7753171194363</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23526,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>374.2818334606677</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -23618,22 +23618,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>70.11380033707866</v>
+        <v>69.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>55.72524664804467</v>
+        <v>54.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>68.53621805555548</v>
+        <v>67.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>63.98090483695654</v>
+        <v>62.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>57.38285596774193</v>
+        <v>56.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>27.80223349726774</v>
+        <v>26.80223349726774</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,31 +23645,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>43.44667544048731</v>
+        <v>42.44667544048731</v>
       </c>
       <c r="L16" t="n">
-        <v>170.6224478299103</v>
+        <v>169.6224478299103</v>
       </c>
       <c r="M16" t="n">
-        <v>265.7535458287794</v>
+        <v>264.7535458287794</v>
       </c>
       <c r="N16" t="n">
-        <v>317.2076654356193</v>
+        <v>316.2076654356193</v>
       </c>
       <c r="O16" t="n">
-        <v>389.2909411281953</v>
+        <v>388.2909411281953</v>
       </c>
       <c r="P16" t="n">
-        <v>441.2227170004086</v>
+        <v>440.2227170004086</v>
       </c>
       <c r="Q16" t="n">
-        <v>175.9931646846114</v>
+        <v>168.0926646846114</v>
       </c>
       <c r="R16" t="n">
-        <v>498.7371443745937</v>
+        <v>497.7371443745937</v>
       </c>
       <c r="S16" t="n">
-        <v>141.1623649487571</v>
+        <v>140.1623649487571</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23684,10 +23684,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>30.44364543010755</v>
+        <v>29.44364543010755</v>
       </c>
       <c r="Y16" t="n">
-        <v>70.46535284946236</v>
+        <v>69.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23706,7 +23706,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>35.51351715729894</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -23757,7 +23757,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>35.51351715729896</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -23885,28 +23885,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>79.62244782991033</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>174.7535458287794</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>226.2076654356193</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>192.0281399868593</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>397.605266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>325.1688976043274</v>
       </c>
       <c r="S19" t="n">
-        <v>50.16236494875707</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23940,7 +23940,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>35.51351715729896</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23997,7 +23997,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>35.51351715729891</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -24125,22 +24125,22 @@
         <v>79.62244782991033</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>174.7535458287794</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>226.2076654356193</v>
       </c>
       <c r="O22" t="n">
-        <v>298.2909411281953</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>192.0281399868595</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>294.6984101230626</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>50.16236494875707</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>16.10951715729909</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5863171572986801</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24359,28 +24359,28 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>79.62244782991033</v>
+        <v>79.6224478299103</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>174.7535458287794</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>226.2076654356193</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>192.0281399868591</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>185.252206876664</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>407.7371443745937</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>50.16236494875707</v>
+        <v>50.1623649487571</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24414,7 +24414,7 @@
         <v>232.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>193.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>187.3632896068686</v>
@@ -24423,10 +24423,10 @@
         <v>187.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>186.2186788196796</v>
+        <v>186.2186788196795</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>185.4927642311656</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24468,16 +24468,16 @@
         <v>432.1782010712237</v>
       </c>
       <c r="V26" t="n">
-        <v>14.85102416681605</v>
+        <v>193.5400936510538</v>
       </c>
       <c r="W26" t="n">
-        <v>286.5770327533453</v>
+        <v>23.37347598091651</v>
       </c>
       <c r="X26" t="n">
         <v>375.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>294.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24490,7 +24490,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>144.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -24499,13 +24499,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>99.49630294894845</v>
       </c>
       <c r="G27" t="n">
         <v>108.451309459933</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.3844268090626</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24538,10 +24538,10 @@
         <v>312.3784765376623</v>
       </c>
       <c r="S27" t="n">
-        <v>124.7951275312694</v>
+        <v>244.2103207193283</v>
       </c>
       <c r="T27" t="n">
-        <v>187.1960105005327</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -24566,16 +24566,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>70.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>55.72524664804467</v>
       </c>
       <c r="D28" t="n">
         <v>68.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>18.37021502985027</v>
+        <v>63.98090483695654</v>
       </c>
       <c r="F28" t="n">
         <v>57.38285596774193</v>
@@ -24593,7 +24593,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>43.4466754404873</v>
+        <v>43.44667544048731</v>
       </c>
       <c r="L28" t="n">
         <v>170.6224478299103</v>
@@ -24614,10 +24614,10 @@
         <v>488.605266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>498.7371443745936</v>
+        <v>186.125042633607</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>141.1623649487571</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24645,7 +24645,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>238.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>206.4745782429939</v>
@@ -24654,13 +24654,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>161.3632896068686</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>160.2186788196795</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24696,16 +24696,16 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>239.5726904153882</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>341.3174510752975</v>
+        <v>72.12299315621652</v>
       </c>
       <c r="U29" t="n">
-        <v>8.178201071213493</v>
+        <v>406.1782010712237</v>
       </c>
       <c r="V29" t="n">
-        <v>129.3767754082864</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>395.3734759809475</v>
@@ -24733,7 +24733,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>99.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -24742,7 +24742,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>86.38442680906265</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -24772,7 +24772,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>286.3784765376623</v>
+        <v>195.038418533694</v>
       </c>
       <c r="S30" t="n">
         <v>218.2103207193283</v>
@@ -24787,7 +24787,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>111.3207553186922</v>
+        <v>189.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -24818,7 +24818,7 @@
         <v>31.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>1.802233497267737</v>
+        <v>1.802233497267736</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24830,28 +24830,28 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>17.44667544048731</v>
+        <v>17.4466754404873</v>
       </c>
       <c r="L31" t="n">
         <v>144.6224478299103</v>
       </c>
       <c r="M31" t="n">
-        <v>39.59289822770771</v>
+        <v>239.7535458287794</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>291.2076654356193</v>
       </c>
       <c r="O31" t="n">
         <v>363.2909411281953</v>
       </c>
       <c r="P31" t="n">
-        <v>415.2227170004086</v>
+        <v>321.8544039637272</v>
       </c>
       <c r="Q31" t="n">
         <v>462.605266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>472.7371443745937</v>
+        <v>74.73714437458403</v>
       </c>
       <c r="S31" t="n">
         <v>115.1623649487571</v>
@@ -24885,22 +24885,22 @@
         <v>238.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>206.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>167.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>161.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>161.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>160.2186788196796</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>159.4927642311656</v>
+        <v>120.2031519288855</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>239.5726904153883</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>341.3174510752975</v>
@@ -24942,16 +24942,16 @@
         <v>406.1782010712237</v>
       </c>
       <c r="V32" t="n">
-        <v>229.0791002740712</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>349.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>268.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -24967,7 +24967,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>8.332039217926479</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -24976,7 +24976,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>82.451309459933</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -25024,7 +25024,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>189.3731429098285</v>
+        <v>115.25387266784</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -25052,10 +25052,10 @@
         <v>37.98090483695654</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>31.38285596774193</v>
       </c>
       <c r="G34" t="n">
-        <v>1.802233497267736</v>
+        <v>1.802233497267737</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -25067,7 +25067,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>17.4466754404873</v>
+        <v>17.44667544048731</v>
       </c>
       <c r="L34" t="n">
         <v>144.6224478299103</v>
@@ -25082,16 +25082,16 @@
         <v>363.2909411281953</v>
       </c>
       <c r="P34" t="n">
-        <v>397.702612780927</v>
+        <v>415.2227170004086</v>
       </c>
       <c r="Q34" t="n">
-        <v>64.60526642559279</v>
+        <v>462.605266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>472.7371443745936</v>
+        <v>74.73714437458402</v>
       </c>
       <c r="S34" t="n">
-        <v>115.1623649487571</v>
+        <v>21.79405191207579</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25109,7 +25109,7 @@
         <v>4.443645430107551</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>44.46535284946236</v>
       </c>
     </row>
     <row r="35">
@@ -25119,13 +25119,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>238.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>206.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>167.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>161.3632896068686</v>
@@ -25137,7 +25137,7 @@
         <v>160.2186788196796</v>
       </c>
       <c r="H35" t="n">
-        <v>159.4927642311656</v>
+        <v>14.75813052241125</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,22 +25170,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>239.5726904153883</v>
       </c>
       <c r="T35" t="n">
         <v>341.3174510752975</v>
       </c>
       <c r="U35" t="n">
-        <v>8.178201071213493</v>
+        <v>406.1782010712237</v>
       </c>
       <c r="V35" t="n">
-        <v>386.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>395.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>323.4266034972728</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25261,13 +25261,13 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>41.31378936162059</v>
+        <v>189.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>156.3913927661343</v>
+        <v>8.332039217944413</v>
       </c>
     </row>
     <row r="37">
@@ -25322,13 +25322,13 @@
         <v>415.2227170004086</v>
       </c>
       <c r="Q37" t="n">
-        <v>369.2369533889121</v>
+        <v>462.605266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>74.73714437458847</v>
+        <v>96.53119628665979</v>
       </c>
       <c r="S37" t="n">
-        <v>115.1623649487571</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25356,25 +25356,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>238.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>206.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>167.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>161.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>161.8896287080119</v>
       </c>
       <c r="G38" t="n">
-        <v>160.2186788196796</v>
+        <v>160.2186788196795</v>
       </c>
       <c r="H38" t="n">
-        <v>159.4927642311656</v>
+        <v>15.53441535866474</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25410,16 +25410,16 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>341.3174510752975</v>
       </c>
       <c r="U38" t="n">
-        <v>8.17820107121122</v>
+        <v>406.1782010712237</v>
       </c>
       <c r="V38" t="n">
-        <v>216.5562416384517</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>395.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>349.2818334606677</v>
@@ -25441,19 +25441,19 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>104.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>99.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>96.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>82.45130945993299</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>86.38442680906263</v>
+        <v>8.332039217944512</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -25483,10 +25483,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>232.2122166582577</v>
+        <v>286.3784765376623</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>218.2103207193283</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -25498,7 +25498,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>189.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -25514,13 +25514,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>44.11380033707866</v>
       </c>
       <c r="C40" t="n">
         <v>29.72524664804467</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>42.53621805555548</v>
       </c>
       <c r="E40" t="n">
         <v>37.98090483695654</v>
@@ -25529,7 +25529,7 @@
         <v>31.38285596774193</v>
       </c>
       <c r="G40" t="n">
-        <v>1.802233497267736</v>
+        <v>1.802233497267737</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>17.4466754404873</v>
+        <v>17.44667544048731</v>
       </c>
       <c r="L40" t="n">
         <v>144.6224478299103</v>
@@ -25559,10 +25559,10 @@
         <v>415.2227170004086</v>
       </c>
       <c r="Q40" t="n">
-        <v>173.0493367302982</v>
+        <v>462.605266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>472.7371443745936</v>
+        <v>96.53119628665979</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>96.03989531070653</v>
       </c>
       <c r="S41" t="n">
         <v>361.5726904153883</v>
@@ -25650,16 +25650,16 @@
         <v>463.3174510752975</v>
       </c>
       <c r="U41" t="n">
-        <v>130.1782010712128</v>
+        <v>130.1782010711855</v>
       </c>
       <c r="V41" t="n">
-        <v>110.8510241668142</v>
+        <v>166.605803950121</v>
       </c>
       <c r="W41" t="n">
-        <v>119.3734759809382</v>
+        <v>119.3734759809116</v>
       </c>
       <c r="X41" t="n">
-        <v>225.0765085545733</v>
+        <v>73.28183346063179</v>
       </c>
       <c r="Y41" t="n">
         <v>390.3174326828064</v>
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>263.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>240.0999124455193</v>
@@ -25684,13 +25684,13 @@
         <v>221.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>218.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>204.451309459933</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>208.3844268090626</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,19 +25720,19 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>10.37847653764754</v>
+        <v>408.3784765376623</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>75.36668349262413</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>279.1913974960358</v>
       </c>
       <c r="V42" t="n">
-        <v>151.0402129269777</v>
+        <v>293.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>311.3731429098285</v>
@@ -25805,13 +25805,13 @@
         <v>237.1623649487571</v>
       </c>
       <c r="T43" t="n">
-        <v>87.99210748986427</v>
+        <v>65.39348246343238</v>
       </c>
       <c r="U43" t="n">
-        <v>29.94521094658909</v>
+        <v>29.94521094658907</v>
       </c>
       <c r="V43" t="n">
-        <v>78.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>105.3728098387097</v>
@@ -25820,7 +25820,7 @@
         <v>126.4436454301076</v>
       </c>
       <c r="Y43" t="n">
-        <v>65.69641760681426</v>
+        <v>166.4653528494624</v>
       </c>
     </row>
     <row r="44">
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>390.9993129555745</v>
+        <v>391.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>358.4745782429939</v>
+        <v>359.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>233.9499893610712</v>
+        <v>320.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>314.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>313.8896287080119</v>
+        <v>314.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>312.2186788196796</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>312.4927642311656</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,28 +25878,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>126.0398953107065</v>
+        <v>127.0398953107065</v>
       </c>
       <c r="S44" t="n">
-        <v>391.5726904153883</v>
+        <v>392.5726904153883</v>
       </c>
       <c r="T44" t="n">
-        <v>493.3174510752975</v>
+        <v>494.3174510752975</v>
       </c>
       <c r="U44" t="n">
-        <v>160.1782010712126</v>
+        <v>163.1516596740904</v>
       </c>
       <c r="V44" t="n">
-        <v>538.8510241668239</v>
+        <v>141.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>547.3734759809475</v>
+        <v>548.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>103.2818334606608</v>
+        <v>104.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>420.3174326828064</v>
+        <v>421.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25909,28 +25909,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>293.5565566463266</v>
+        <v>294.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>270.0999124455193</v>
+        <v>271.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>256.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>251.6720972219126</v>
+        <v>183.8763191914392</v>
       </c>
       <c r="F45" t="n">
-        <v>248.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>238.3844268090626</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>116.2028009856881</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25957,28 +25957,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>438.3784765376623</v>
+        <v>439.3784765376623</v>
       </c>
       <c r="S45" t="n">
-        <v>370.2103207193283</v>
+        <v>371.2103207193283</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>314.1960105005327</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>310.1913974960358</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>324.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>22.45154359170812</v>
+        <v>342.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>328.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>308.3913927661343</v>
+        <v>309.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -25988,76 +25988,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>196.1138003370787</v>
+        <v>197.1138003370787</v>
       </c>
       <c r="C46" t="n">
-        <v>181.7252466480447</v>
+        <v>182.7252466480447</v>
       </c>
       <c r="D46" t="n">
-        <v>194.5362180555555</v>
+        <v>195.5362180555555</v>
       </c>
       <c r="E46" t="n">
-        <v>189.9809048369565</v>
+        <v>190.9809048369565</v>
       </c>
       <c r="F46" t="n">
-        <v>183.3828559677419</v>
+        <v>184.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>153.8022334972677</v>
+        <v>154.8022334972677</v>
       </c>
       <c r="H46" t="n">
-        <v>135.6227326589957</v>
+        <v>136.6227326589957</v>
       </c>
       <c r="I46" t="n">
-        <v>78.36670152175762</v>
+        <v>79.36670152175762</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>169.4466754404873</v>
+        <v>170.4466754404873</v>
       </c>
       <c r="L46" t="n">
-        <v>296.6224478299103</v>
+        <v>297.6224478299103</v>
       </c>
       <c r="M46" t="n">
-        <v>391.7535458287794</v>
+        <v>392.7535458287794</v>
       </c>
       <c r="N46" t="n">
-        <v>443.2076654356193</v>
+        <v>373.8218301929712</v>
       </c>
       <c r="O46" t="n">
-        <v>515.2909411281953</v>
+        <v>516.2909411281953</v>
       </c>
       <c r="P46" t="n">
-        <v>567.2227170004086</v>
+        <v>568.2227170004086</v>
       </c>
       <c r="Q46" t="n">
-        <v>543.2393311829499</v>
+        <v>615.605266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>624.7371443745936</v>
+        <v>625.7371443745936</v>
       </c>
       <c r="S46" t="n">
-        <v>267.1623649487571</v>
+        <v>268.1623649487571</v>
       </c>
       <c r="T46" t="n">
-        <v>117.9921074898643</v>
+        <v>118.9921074898643</v>
       </c>
       <c r="U46" t="n">
-        <v>59.94521094658909</v>
+        <v>60.94521094658909</v>
       </c>
       <c r="V46" t="n">
-        <v>108.1703102162162</v>
+        <v>109.1703102162162</v>
       </c>
       <c r="W46" t="n">
-        <v>135.3728098387097</v>
+        <v>136.3728098387097</v>
       </c>
       <c r="X46" t="n">
-        <v>156.4436454301076</v>
+        <v>157.4436454301076</v>
       </c>
       <c r="Y46" t="n">
-        <v>196.4653528494624</v>
+        <v>197.4653528494624</v>
       </c>
     </row>
   </sheetData>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1144964.307420907</v>
+        <v>1144964.307420906</v>
       </c>
     </row>
     <row r="3">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4752751.946837032</v>
+        <v>4754062.617278749</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5713134.724770401</v>
+        <v>5714445.395212117</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6673517.502703767</v>
+        <v>6674828.173145486</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7637260.517786954</v>
+        <v>7637077.749495419</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8330790.4929493</v>
+        <v>8331143.537183017</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9112227.228216218</v>
+        <v>9112580.272449935</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9893565.9482322</v>
+        <v>9893918.992465913</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10674904.66824819</v>
+        <v>10675257.7124819</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11456243.38826418</v>
+        <v>11456596.43249789</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12007897.97523676</v>
+        <v>12008251.01947048</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12499899.88166028</v>
+        <v>12498261.23603399</v>
       </c>
     </row>
   </sheetData>
@@ -26269,19 +26269,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1215369.181494</v>
+      </c>
+      <c r="C2" t="n">
         <v>1215369.181494001</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1215369.181494</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1215369.181494001</v>
       </c>
       <c r="E2" t="n">
         <v>1051787.933154168</v>
       </c>
       <c r="F2" t="n">
-        <v>1058681.619954169</v>
+        <v>1060330.527929232</v>
       </c>
       <c r="G2" t="n">
         <v>1208223.494819402</v>
@@ -26290,28 +26290,28 @@
         <v>1208223.494819402</v>
       </c>
       <c r="I2" t="n">
-        <v>1210934.194811402</v>
+        <v>1209729.439259401</v>
       </c>
       <c r="J2" t="n">
-        <v>924073.087110405</v>
+        <v>924073.0871104016</v>
       </c>
       <c r="K2" t="n">
-        <v>982974.5187297874</v>
+        <v>982974.5187297855</v>
       </c>
       <c r="L2" t="n">
-        <v>982974.5187297872</v>
+        <v>982974.5187297855</v>
       </c>
       <c r="M2" t="n">
-        <v>982974.5187297877</v>
+        <v>982974.5187297846</v>
       </c>
       <c r="N2" t="n">
-        <v>982974.5187297867</v>
+        <v>982974.5187297855</v>
       </c>
       <c r="O2" t="n">
-        <v>694140.3705392533</v>
+        <v>694140.3705392521</v>
       </c>
       <c r="P2" t="n">
-        <v>618970.1403392534</v>
+        <v>616464.4659992512</v>
       </c>
     </row>
     <row r="3">
@@ -26333,25 +26333,25 @@
         <v>170400</v>
       </c>
       <c r="F3" t="n">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="G3" t="n">
-        <v>72800</v>
+        <v>72000</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3168</v>
+        <v>1760</v>
       </c>
       <c r="J3" t="n">
-        <v>234528.0000000016</v>
+        <v>235936</v>
       </c>
       <c r="K3" t="n">
-        <v>24000</v>
+        <v>24800</v>
       </c>
       <c r="L3" t="n">
-        <v>72800</v>
+        <v>72000</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>610855.6087870573</v>
+        <v>606911.3795032545</v>
       </c>
       <c r="C4" t="n">
-        <v>609122.516407321</v>
+        <v>605178.2871235184</v>
       </c>
       <c r="D4" t="n">
-        <v>607387.0729795995</v>
+        <v>603442.8436957968</v>
       </c>
       <c r="E4" t="n">
-        <v>508962.0535581453</v>
+        <v>505059.5028188385</v>
       </c>
       <c r="F4" t="n">
-        <v>511566.0426588866</v>
+        <v>508610.124978587</v>
       </c>
       <c r="G4" t="n">
-        <v>595989.682927325</v>
+        <v>592087.1321880183</v>
       </c>
       <c r="H4" t="n">
-        <v>594261.0668104909</v>
+        <v>590358.5160711842</v>
       </c>
       <c r="I4" t="n">
-        <v>593733.4118703613</v>
+        <v>589281.2618174503</v>
       </c>
       <c r="J4" t="n">
-        <v>440080.1179253687</v>
+        <v>437054.6834986308</v>
       </c>
       <c r="K4" t="n">
-        <v>472328.5300949453</v>
+        <v>469300.9347340986</v>
       </c>
       <c r="L4" t="n">
-        <v>470915.0867023615</v>
+        <v>467887.4913415147</v>
       </c>
       <c r="M4" t="n">
-        <v>469499.6231161406</v>
+        <v>466472.0277552939</v>
       </c>
       <c r="N4" t="n">
-        <v>468082.1243286534</v>
+        <v>465054.5289678067</v>
       </c>
       <c r="O4" t="n">
-        <v>305627.7293396324</v>
+        <v>302602.2949128944</v>
       </c>
       <c r="P4" t="n">
-        <v>263221.9709464278</v>
+        <v>258807.2752024118</v>
       </c>
     </row>
     <row r="5">
@@ -26437,7 +26437,7 @@
         <v>63083.897</v>
       </c>
       <c r="F5" t="n">
-        <v>63420.173</v>
+        <v>63504.242</v>
       </c>
       <c r="G5" t="n">
         <v>71070.452</v>
@@ -26446,28 +26446,28 @@
         <v>71070.452</v>
       </c>
       <c r="I5" t="n">
-        <v>71617.652</v>
+        <v>71374.452</v>
       </c>
       <c r="J5" t="n">
-        <v>45362.57300000028</v>
+        <v>45362.573</v>
       </c>
       <c r="K5" t="n">
-        <v>47548.36700000028</v>
+        <v>47548.367</v>
       </c>
       <c r="L5" t="n">
-        <v>47548.36700000028</v>
+        <v>47548.367</v>
       </c>
       <c r="M5" t="n">
-        <v>47548.36700000028</v>
+        <v>47548.367</v>
       </c>
       <c r="N5" t="n">
-        <v>47548.36700000028</v>
+        <v>47548.367</v>
       </c>
       <c r="O5" t="n">
-        <v>37291.94900000028</v>
+        <v>37291.949</v>
       </c>
       <c r="P5" t="n">
-        <v>34769.87900000028</v>
+        <v>34685.81</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150418.7727069433</v>
+        <v>154363.0019907458</v>
       </c>
       <c r="C6" t="n">
-        <v>527441.8650866793</v>
+        <v>531386.0943704823</v>
       </c>
       <c r="D6" t="n">
-        <v>529177.3085144013</v>
+        <v>533121.5377982031</v>
       </c>
       <c r="E6" t="n">
-        <v>309341.9825960228</v>
+        <v>313244.5333353298</v>
       </c>
       <c r="F6" t="n">
-        <v>480495.4042952821</v>
+        <v>484216.1609506445</v>
       </c>
       <c r="G6" t="n">
-        <v>468363.3598920768</v>
+        <v>473065.9106313835</v>
       </c>
       <c r="H6" t="n">
-        <v>542891.9760089113</v>
+        <v>546794.5267482175</v>
       </c>
       <c r="I6" t="n">
-        <v>542415.1309410403</v>
+        <v>547313.725441951</v>
       </c>
       <c r="J6" t="n">
-        <v>204102.3961850344</v>
+        <v>205719.8306117708</v>
       </c>
       <c r="K6" t="n">
-        <v>439097.6216348418</v>
+        <v>441325.2169956869</v>
       </c>
       <c r="L6" t="n">
-        <v>391711.0650274254</v>
+        <v>395538.6603882707</v>
       </c>
       <c r="M6" t="n">
-        <v>465926.5286136468</v>
+        <v>468954.1239744908</v>
       </c>
       <c r="N6" t="n">
-        <v>467344.027401133</v>
+        <v>470371.6227619788</v>
       </c>
       <c r="O6" t="n">
-        <v>351220.6921996207</v>
+        <v>354246.1266263576</v>
       </c>
       <c r="P6" t="n">
-        <v>320978.2903928253</v>
+        <v>322971.3807968394</v>
       </c>
     </row>
   </sheetData>
@@ -26767,7 +26767,7 @@
         <v>213</v>
       </c>
       <c r="F2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G2" t="n">
         <v>308</v>
@@ -26797,7 +26797,7 @@
         <v>121</v>
       </c>
       <c r="P2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -26880,28 +26880,28 @@
         <v>695</v>
       </c>
       <c r="I4" t="n">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J4" t="n">
-        <v>398.0000000000047</v>
+        <v>398</v>
       </c>
       <c r="K4" t="n">
-        <v>398.0000000000047</v>
+        <v>398</v>
       </c>
       <c r="L4" t="n">
-        <v>398.0000000000047</v>
+        <v>398</v>
       </c>
       <c r="M4" t="n">
-        <v>398.0000000000047</v>
+        <v>398</v>
       </c>
       <c r="N4" t="n">
-        <v>398.0000000000047</v>
+        <v>398</v>
       </c>
       <c r="O4" t="n">
-        <v>398.0000000000047</v>
+        <v>398</v>
       </c>
       <c r="P4" t="n">
-        <v>398.0000000000047</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -26984,31 +26984,31 @@
         <v>213</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>122</v>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -27097,10 +27097,10 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27216,10 +27216,10 @@
         <v>213</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27231,7 +27231,7 @@
         <v>122</v>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>76.82669694048604</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
@@ -27484,13 +27484,13 @@
         <v>217.0398953107065</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>400</v>
-      </c>
-      <c r="U2" t="n">
-        <v>76.82669694048604</v>
       </c>
       <c r="V2" t="n">
         <v>400</v>
@@ -27512,19 +27512,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>250.4943658794744</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.451309459933</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
+        <v>205.5740515710247</v>
+      </c>
+      <c r="U3" t="n">
         <v>400</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -27606,19 +27606,19 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.8022334972677</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>381.4237974528672</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>48.42200066722171</v>
+        <v>18.18504719656352</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>260.4466754404873</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,7 +27645,7 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>208.9921074898643</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>150.9452109465891</v>
@@ -27657,7 +27657,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27670,10 +27670,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27685,13 +27685,13 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
+        <v>293.8665922511929</v>
+      </c>
+      <c r="H5" t="n">
         <v>400</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
-        <v>129.3131797831871</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,10 +27721,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
-        <v>164.5534124680055</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>301.9480717479061</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>136.2874160338758</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27812,13 +27812,13 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>347.2730871250039</v>
       </c>
     </row>
     <row r="7">
@@ -27828,22 +27828,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8022334972677</v>
       </c>
       <c r="H7" t="n">
         <v>226.6227326589957</v>
@@ -27852,10 +27852,10 @@
         <v>169.3667015217576</v>
       </c>
       <c r="J7" t="n">
-        <v>114.8161612240189</v>
+        <v>18.18504719656352</v>
       </c>
       <c r="K7" t="n">
-        <v>260.4466754404873</v>
+        <v>323.1138232186998</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,16 +27882,16 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>208.9921074898643</v>
       </c>
       <c r="U7" t="n">
         <v>150.9452109465891</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27913,7 +27913,7 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
         <v>400</v>
@@ -27922,10 +27922,10 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>400</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27961,10 +27961,10 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>293.8665922511931</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>400</v>
+        <v>293.8665922511924</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>137.0455877849268</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -27998,10 +27998,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.451309459933</v>
       </c>
       <c r="H9" t="n">
         <v>329.3844268090626</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>136.2874160338758</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>341.252860371035</v>
       </c>
     </row>
     <row r="10">
@@ -28074,7 +28074,7 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
@@ -28089,13 +28089,13 @@
         <v>169.3667015217576</v>
       </c>
       <c r="J10" t="n">
-        <v>18.18504719656352</v>
+        <v>297.6033453160171</v>
       </c>
       <c r="K10" t="n">
-        <v>260.4466754404873</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>387.6224478299103</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>358.1623649487571</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>368.694236064853</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9452109465891</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
@@ -28247,7 +28247,7 @@
         <v>213</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="K12" t="n">
         <v>213</v>
@@ -28256,16 +28256,16 @@
         <v>213</v>
       </c>
       <c r="M12" t="n">
-        <v>213</v>
+        <v>29.03316867746966</v>
       </c>
       <c r="N12" t="n">
         <v>213</v>
       </c>
       <c r="O12" t="n">
-        <v>29.03316867746963</v>
+        <v>213</v>
       </c>
       <c r="P12" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>213</v>
@@ -28381,25 +28381,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I14" t="n">
         <v>129.3131797831871</v>
@@ -28429,28 +28429,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>217</v>
+        <v>217.0398953107065</v>
       </c>
       <c r="S14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="V14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="W14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="X14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15">
@@ -28460,76 +28460,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>135.5103648819382</v>
       </c>
       <c r="M15" t="n">
-        <v>156.8149256410443</v>
+        <v>218</v>
       </c>
       <c r="N15" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="S15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="V15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="W15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="X15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16">
@@ -28539,76 +28539,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="S16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="V16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="W16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="X16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
@@ -28700,7 +28700,7 @@
         <v>308</v>
       </c>
       <c r="C18" t="n">
-        <v>308</v>
+        <v>36.12974691991315</v>
       </c>
       <c r="D18" t="n">
         <v>308</v>
@@ -28748,7 +28748,7 @@
         <v>308</v>
       </c>
       <c r="S18" t="n">
-        <v>36.12974691991343</v>
+        <v>308</v>
       </c>
       <c r="T18" t="n">
         <v>308</v>
@@ -28946,7 +28946,7 @@
         <v>308</v>
       </c>
       <c r="F21" t="n">
-        <v>172.4171629537892</v>
+        <v>308</v>
       </c>
       <c r="G21" t="n">
         <v>308</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>136.2874160338758</v>
       </c>
       <c r="R21" t="n">
         <v>308</v>
@@ -28988,7 +28988,7 @@
         <v>308</v>
       </c>
       <c r="T21" t="n">
-        <v>308</v>
+        <v>36.12974691991337</v>
       </c>
       <c r="U21" t="n">
         <v>308</v>
@@ -29180,7 +29180,7 @@
         <v>308</v>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>36.12974691991303</v>
       </c>
       <c r="F24" t="n">
         <v>308</v>
@@ -29237,7 +29237,7 @@
         <v>308</v>
       </c>
       <c r="X24" t="n">
-        <v>36.1297469199132</v>
+        <v>308</v>
       </c>
       <c r="Y24" t="n">
         <v>308</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>137.1401530353735</v>
+        <v>137.1401530353552</v>
       </c>
       <c r="R27" t="n">
         <v>217</v>
@@ -29666,7 +29666,7 @@
         <v>243</v>
       </c>
       <c r="I30" t="n">
-        <v>208.0555379871859</v>
+        <v>207.2028009856882</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>136.2874160338758</v>
+        <v>137.1401530353552</v>
       </c>
       <c r="R30" t="n">
         <v>243</v>
@@ -29903,7 +29903,7 @@
         <v>243</v>
       </c>
       <c r="I33" t="n">
-        <v>207.2028009856882</v>
+        <v>208.0555379871674</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>137.1401530353733</v>
+        <v>136.2874160338758</v>
       </c>
       <c r="R33" t="n">
         <v>243</v>
@@ -30140,7 +30140,7 @@
         <v>243</v>
       </c>
       <c r="I36" t="n">
-        <v>208.0555379871856</v>
+        <v>207.2028009856882</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>136.2874160338758</v>
+        <v>137.1401530353552</v>
       </c>
       <c r="R36" t="n">
         <v>243</v>
@@ -30377,7 +30377,7 @@
         <v>243</v>
       </c>
       <c r="I39" t="n">
-        <v>208.0555379871859</v>
+        <v>208.0555379871674</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30620,7 +30620,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8527370014977294</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -30629,7 +30629,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.8527370014793973</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -30751,28 +30751,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,28 +30799,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y44" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45">
@@ -30830,40 +30830,40 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.8527370014792552</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8527370014977009</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -30875,31 +30875,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y45" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="W46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -34892,19 +34892,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1977665027323</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>173.3772673410043</v>
+        <v>154.8010647938715</v>
       </c>
       <c r="I4" t="n">
         <v>230.6332984782424</v>
       </c>
       <c r="J4" t="n">
-        <v>30.23695347065819</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>139.5533245595127</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>12.3775521700897</v>
@@ -34931,7 +34931,7 @@
         <v>41.8376350512429</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>191.0078925101357</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34943,7 +34943,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34986,7 +34986,7 @@
         <v>695</v>
       </c>
       <c r="L5" t="n">
-        <v>695</v>
+        <v>694.9999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>695</v>
@@ -35114,22 +35114,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1977665027323</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -35138,10 +35138,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>96.63111402745537</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>62.6671477782125</v>
       </c>
       <c r="L7" t="n">
         <v>12.37755217008968</v>
@@ -35168,16 +35168,16 @@
         <v>41.83763505124293</v>
       </c>
       <c r="T7" t="n">
-        <v>191.0078925101357</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35360,7 +35360,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -35375,13 +35375,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>279.4182981194536</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>139.5533245595127</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>12.3775521700897</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>41.8376350512429</v>
       </c>
       <c r="T10" t="n">
-        <v>159.7021285749887</v>
+        <v>191.0078925101357</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0547890534109</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -35533,7 +35533,7 @@
         <v>5.797199014311845</v>
       </c>
       <c r="J12" t="n">
-        <v>152.4396817093738</v>
+        <v>365.4396817093739</v>
       </c>
       <c r="K12" t="n">
         <v>450.6460999238102</v>
@@ -35542,16 +35542,16 @@
         <v>549.6731678015171</v>
       </c>
       <c r="M12" t="n">
-        <v>372.9800421645043</v>
+        <v>189.0132108419739</v>
       </c>
       <c r="N12" t="n">
         <v>422.5894369011077</v>
       </c>
       <c r="O12" t="n">
-        <v>339.0665868066311</v>
+        <v>523.0334181291614</v>
       </c>
       <c r="P12" t="n">
-        <v>381.7046082882381</v>
+        <v>168.7046082882381</v>
       </c>
       <c r="Q12" t="n">
         <v>76.71258396612419</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>440.9826650144332</v>
+        <v>10.67792842827651</v>
       </c>
       <c r="K14" t="n">
         <v>695</v>
       </c>
       <c r="L14" t="n">
-        <v>85.00986934673369</v>
+        <v>141.7466098736763</v>
       </c>
       <c r="M14" t="n">
         <v>610.5987772044975</v>
@@ -35712,7 +35712,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q14" t="n">
-        <v>127.6342270537287</v>
+        <v>501.2022231129425</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,31 +35767,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9.797199014311845</v>
+        <v>10.79719901431185</v>
       </c>
       <c r="J15" t="n">
-        <v>369.4396817093739</v>
+        <v>370.4396817093739</v>
       </c>
       <c r="K15" t="n">
-        <v>237.6460999238102</v>
+        <v>455.6460999238102</v>
       </c>
       <c r="L15" t="n">
-        <v>336.6731678015172</v>
+        <v>472.1835326834553</v>
       </c>
       <c r="M15" t="n">
-        <v>316.7949678055486</v>
+        <v>377.9800421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>426.5894369011077</v>
+        <v>209.5894369011077</v>
       </c>
       <c r="O15" t="n">
-        <v>527.0334181291614</v>
+        <v>310.0334181291615</v>
       </c>
       <c r="P15" t="n">
-        <v>385.7046082882381</v>
+        <v>386.7046082882381</v>
       </c>
       <c r="Q15" t="n">
-        <v>80.71258396612419</v>
+        <v>81.71258396612419</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35846,10 +35846,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>47.63329847824238</v>
+        <v>48.63329847824238</v>
       </c>
       <c r="J16" t="n">
-        <v>198.8149528034365</v>
+        <v>199.8149528034365</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -35879,13 +35879,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>8.007892510135729</v>
+        <v>9.007892510135729</v>
       </c>
       <c r="U16" t="n">
-        <v>66.05478905341091</v>
+        <v>67.05478905341091</v>
       </c>
       <c r="V16" t="n">
-        <v>17.82968978378381</v>
+        <v>18.82968978378381</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -35928,7 +35928,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>67.4146689552192</v>
+        <v>440.9826650144332</v>
       </c>
       <c r="K17" t="n">
         <v>695</v>
@@ -35949,7 +35949,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q17" t="n">
-        <v>501.2022231129425</v>
+        <v>127.6342270537287</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>10.67792842827651</v>
+        <v>440.9826650144332</v>
       </c>
       <c r="K20" t="n">
         <v>695</v>
       </c>
       <c r="L20" t="n">
-        <v>695</v>
+        <v>212.6440964004626</v>
       </c>
       <c r="M20" t="n">
         <v>610.5987772044975</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="O20" t="n">
         <v>20.51591937063117</v>
       </c>
       <c r="P20" t="n">
-        <v>695</v>
+        <v>77.17773392916783</v>
       </c>
       <c r="Q20" t="n">
-        <v>25.12656691578649</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36405,16 +36405,16 @@
         <v>440.9826650144332</v>
       </c>
       <c r="K23" t="n">
-        <v>68.52382914572866</v>
+        <v>700</v>
       </c>
       <c r="L23" t="n">
-        <v>704.0000000000001</v>
+        <v>222.4420761984422</v>
       </c>
       <c r="M23" t="n">
         <v>610.5987772044975</v>
       </c>
       <c r="N23" t="n">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="O23" t="n">
         <v>20.51591937063117</v>
@@ -36423,7 +36423,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q23" t="n">
-        <v>161.7566308910971</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36554,7 +36554,7 @@
         <v>63.19776650273226</v>
       </c>
       <c r="H25" t="n">
-        <v>81.37726734100433</v>
+        <v>81.37726734100434</v>
       </c>
       <c r="I25" t="n">
         <v>138.6332984782424</v>
@@ -36563,7 +36563,7 @@
         <v>289.8149528034365</v>
       </c>
       <c r="K25" t="n">
-        <v>47.55332455951269</v>
+        <v>47.5533245595127</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>99.00789251013573</v>
+        <v>99.00789251013572</v>
       </c>
       <c r="U25" t="n">
         <v>157.0547890534109</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>398.0000000000058</v>
+        <v>398.0000000000116</v>
       </c>
       <c r="K26" t="n">
         <v>68.52382914572866</v>
       </c>
       <c r="L26" t="n">
-        <v>85.00986934673364</v>
+        <v>215.7017094736299</v>
       </c>
       <c r="M26" t="n">
-        <v>398.0000000000058</v>
+        <v>398.0000000000116</v>
       </c>
       <c r="N26" t="n">
-        <v>130.6918401269318</v>
+        <v>398.0000000000116</v>
       </c>
       <c r="O26" t="n">
         <v>20.51591937063117</v>
@@ -36660,7 +36660,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q26" t="n">
-        <v>398.0000000000058</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>168.7046082882381</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8527370014977038</v>
+        <v>0.8527370014793302</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36827,10 +36827,10 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>8.007892510135719</v>
+        <v>8.007892510135729</v>
       </c>
       <c r="U28" t="n">
-        <v>66.05478905341093</v>
+        <v>66.05478905341091</v>
       </c>
       <c r="V28" t="n">
         <v>17.82968978378381</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>398.0000000000052</v>
+        <v>398.0000000000097</v>
       </c>
       <c r="K29" t="n">
-        <v>211.2188998938503</v>
+        <v>398</v>
       </c>
       <c r="L29" t="n">
         <v>85.00986934673369</v>
       </c>
       <c r="M29" t="n">
-        <v>398.0000000000052</v>
+        <v>344.8080279591921</v>
       </c>
       <c r="N29" t="n">
-        <v>133.5891280647842</v>
+        <v>398.0000000000097</v>
       </c>
       <c r="O29" t="n">
         <v>20.51591937063117</v>
@@ -36897,7 +36897,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q29" t="n">
-        <v>398.0000000000052</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8527370014977038</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>152.4396817093738</v>
@@ -36976,7 +36976,7 @@
         <v>168.7046082882381</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.8527370014793302</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>16.37726734100433</v>
+        <v>16.37726734100434</v>
       </c>
       <c r="I31" t="n">
         <v>73.63329847824238</v>
@@ -37064,10 +37064,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>34.00789251013573</v>
+        <v>34.00789251013572</v>
       </c>
       <c r="U31" t="n">
-        <v>92.05478905341091</v>
+        <v>92.05478905341093</v>
       </c>
       <c r="V31" t="n">
         <v>43.82968978378381</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>10.67792842827651</v>
+        <v>398.0000000000097</v>
       </c>
       <c r="K32" t="n">
-        <v>68.52382914572864</v>
+        <v>398</v>
       </c>
       <c r="L32" t="n">
-        <v>350.6161397313923</v>
+        <v>85.00986934673369</v>
       </c>
       <c r="M32" t="n">
-        <v>398.0000000000052</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>398.0000000000052</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>20.51591937063117</v>
+        <v>398.0000000000097</v>
       </c>
       <c r="P32" t="n">
-        <v>77.17773392916783</v>
+        <v>398.0000000000097</v>
       </c>
       <c r="Q32" t="n">
-        <v>398.0000000000052</v>
+        <v>44.5016812589663</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.8527370014792477</v>
       </c>
       <c r="J33" t="n">
         <v>152.4396817093738</v>
@@ -37213,7 +37213,7 @@
         <v>168.7046082882381</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8527370014974741</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>16.37726734100434</v>
+        <v>16.37726734100433</v>
       </c>
       <c r="I34" t="n">
         <v>73.63329847824238</v>
@@ -37301,10 +37301,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>34.00789251013572</v>
+        <v>34.00789251013573</v>
       </c>
       <c r="U34" t="n">
-        <v>92.05478905341093</v>
+        <v>92.05478905341091</v>
       </c>
       <c r="V34" t="n">
         <v>43.82968978378381</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>398.0000000000052</v>
+        <v>10.67792842827651</v>
       </c>
       <c r="K35" t="n">
-        <v>68.52382914572866</v>
+        <v>68.52382914572864</v>
       </c>
       <c r="L35" t="n">
-        <v>227.7049400948861</v>
+        <v>350.6161397319487</v>
       </c>
       <c r="M35" t="n">
-        <v>133.5891280647848</v>
+        <v>398.0000000000117</v>
       </c>
       <c r="N35" t="n">
-        <v>398.0000000000052</v>
+        <v>398.0000000000117</v>
       </c>
       <c r="O35" t="n">
         <v>20.51591937063117</v>
@@ -37371,7 +37371,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q35" t="n">
-        <v>398.0000000000052</v>
+        <v>398.0000000000117</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8527370014974741</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>152.4396817093738</v>
@@ -37450,7 +37450,7 @@
         <v>168.7046082882381</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.8527370014793302</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37590,16 +37590,16 @@
         <v>10.67792842827651</v>
       </c>
       <c r="K38" t="n">
-        <v>68.52382914572864</v>
+        <v>334.1300995308806</v>
       </c>
       <c r="L38" t="n">
-        <v>350.6161397313952</v>
+        <v>85.00986934673369</v>
       </c>
       <c r="M38" t="n">
-        <v>398.0000000000052</v>
+        <v>398.0000000000099</v>
       </c>
       <c r="N38" t="n">
-        <v>398.0000000000052</v>
+        <v>398.0000000000099</v>
       </c>
       <c r="O38" t="n">
         <v>20.51591937063117</v>
@@ -37608,7 +37608,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q38" t="n">
-        <v>398.0000000000052</v>
+        <v>398.0000000000099</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8527370014977038</v>
+        <v>0.8527370014792477</v>
       </c>
       <c r="J39" t="n">
         <v>152.4396817093738</v>
@@ -37739,7 +37739,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>16.37726734100434</v>
+        <v>16.37726734100433</v>
       </c>
       <c r="I40" t="n">
         <v>73.63329847824238</v>
@@ -37775,10 +37775,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>34.00789251013572</v>
+        <v>34.00789251013573</v>
       </c>
       <c r="U40" t="n">
-        <v>92.05478905341093</v>
+        <v>92.05478905341091</v>
       </c>
       <c r="V40" t="n">
         <v>43.82968978378381</v>
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>10.67792842827651</v>
+        <v>398.0000000000099</v>
       </c>
       <c r="K41" t="n">
-        <v>398.0000000000047</v>
+        <v>68.52382914572866</v>
       </c>
       <c r="L41" t="n">
         <v>85.00986934673369</v>
       </c>
       <c r="M41" t="n">
-        <v>398.0000000000052</v>
+        <v>130.6918401269009</v>
       </c>
       <c r="N41" t="n">
-        <v>398.0000000000052</v>
+        <v>398.0000000000099</v>
       </c>
       <c r="O41" t="n">
         <v>20.51591937063117</v>
@@ -37845,7 +37845,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q41" t="n">
-        <v>188.5377408443862</v>
+        <v>398.0000000000099</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,7 +37906,7 @@
         <v>152.4396817093738</v>
       </c>
       <c r="K42" t="n">
-        <v>238.4988369253079</v>
+        <v>237.6460999238102</v>
       </c>
       <c r="L42" t="n">
         <v>336.6731678015172</v>
@@ -37915,7 +37915,7 @@
         <v>159.9800421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>209.5894369011077</v>
+        <v>210.442173902587</v>
       </c>
       <c r="O42" t="n">
         <v>310.0334181291615</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>398.0000000000043</v>
+        <v>10.67792842827651</v>
       </c>
       <c r="K44" t="n">
-        <v>68.52382914572866</v>
+        <v>398</v>
       </c>
       <c r="L44" t="n">
-        <v>85.00986934673369</v>
+        <v>85.00986934673364</v>
       </c>
       <c r="M44" t="n">
-        <v>130.6918401269361</v>
+        <v>398.0000000000101</v>
       </c>
       <c r="N44" t="n">
-        <v>398.0000000000043</v>
+        <v>398.0000000000101</v>
       </c>
       <c r="O44" t="n">
         <v>20.51591937063117</v>
@@ -38082,7 +38082,7 @@
         <v>77.17773392916783</v>
       </c>
       <c r="Q44" t="n">
-        <v>398.0000000000043</v>
+        <v>188.5377408443628</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,13 +38143,13 @@
         <v>152.4396817093738</v>
       </c>
       <c r="K45" t="n">
-        <v>237.6460999238102</v>
+        <v>238.4988369252895</v>
       </c>
       <c r="L45" t="n">
         <v>336.6731678015172</v>
       </c>
       <c r="M45" t="n">
-        <v>160.832779166002</v>
+        <v>159.9800421645043</v>
       </c>
       <c r="N45" t="n">
         <v>209.5894369011077</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>72.8149528034365</v>
+        <v>71.8149528034365</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
